--- a/comparar_precios.xlsx
+++ b/comparar_precios.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="301">
   <si>
     <t>Sku</t>
   </si>
@@ -31,9 +31,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>084711</t>
+  </si>
+  <si>
     <t>028138</t>
   </si>
   <si>
+    <t>024399</t>
+  </si>
+  <si>
     <t>981403</t>
   </si>
   <si>
@@ -49,21 +55,24 @@
     <t>145401</t>
   </si>
   <si>
+    <t>534786</t>
+  </si>
+  <si>
+    <t>086627</t>
+  </si>
+  <si>
+    <t>942668</t>
+  </si>
+  <si>
+    <t>772845</t>
+  </si>
+  <si>
     <t>117408</t>
   </si>
   <si>
     <t>117414</t>
   </si>
   <si>
-    <t>785762</t>
-  </si>
-  <si>
-    <t>667427</t>
-  </si>
-  <si>
-    <t>026960</t>
-  </si>
-  <si>
     <t>126616</t>
   </si>
   <si>
@@ -85,6 +94,9 @@
     <t>176638</t>
   </si>
   <si>
+    <t>919698</t>
+  </si>
+  <si>
     <t>812279</t>
   </si>
   <si>
@@ -121,13 +133,13 @@
     <t>909050</t>
   </si>
   <si>
-    <t>056402</t>
-  </si>
-  <si>
-    <t>117418</t>
-  </si>
-  <si>
-    <t>771601</t>
+    <t>463996</t>
+  </si>
+  <si>
+    <t>472179</t>
+  </si>
+  <si>
+    <t>304096</t>
   </si>
   <si>
     <t>117424</t>
@@ -157,9 +169,6 @@
     <t>855281</t>
   </si>
   <si>
-    <t>443149</t>
-  </si>
-  <si>
     <t>308917</t>
   </si>
   <si>
@@ -175,9 +184,6 @@
     <t>325838</t>
   </si>
   <si>
-    <t>444057</t>
-  </si>
-  <si>
     <t>241181</t>
   </si>
   <si>
@@ -199,7 +205,7 @@
     <t>834883</t>
   </si>
   <si>
-    <t>282553</t>
+    <t>974855</t>
   </si>
   <si>
     <t>184283</t>
@@ -226,9 +232,6 @@
     <t>132621</t>
   </si>
   <si>
-    <t>922151</t>
-  </si>
-  <si>
     <t>341189</t>
   </si>
   <si>
@@ -250,15 +253,15 @@
     <t>900911</t>
   </si>
   <si>
-    <t>996798</t>
-  </si>
-  <si>
     <t>817713</t>
   </si>
   <si>
     <t>456336</t>
   </si>
   <si>
+    <t>876119</t>
+  </si>
+  <si>
     <t>447950</t>
   </si>
   <si>
@@ -268,7 +271,10 @@
     <t>004342</t>
   </si>
   <si>
-    <t>751695</t>
+    <t>543252</t>
+  </si>
+  <si>
+    <t>236911</t>
   </si>
   <si>
     <t>282286</t>
@@ -283,15 +289,18 @@
     <t>943123</t>
   </si>
   <si>
+    <t>274669</t>
+  </si>
+  <si>
     <t>186179</t>
   </si>
   <si>
+    <t>930232</t>
+  </si>
+  <si>
     <t>133404</t>
   </si>
   <si>
-    <t>048137</t>
-  </si>
-  <si>
     <t>051232</t>
   </si>
   <si>
@@ -319,30 +328,27 @@
     <t>403710</t>
   </si>
   <si>
-    <t>282216</t>
-  </si>
-  <si>
     <t>713313</t>
   </si>
   <si>
-    <t>345344</t>
-  </si>
-  <si>
-    <t>569780</t>
-  </si>
-  <si>
-    <t>812874</t>
+    <t>903727</t>
   </si>
   <si>
     <t>270015</t>
   </si>
   <si>
-    <t>494954</t>
+    <t>126824</t>
+  </si>
+  <si>
+    <t>507226</t>
   </si>
   <si>
     <t>620611</t>
   </si>
   <si>
+    <t>740443</t>
+  </si>
+  <si>
     <t>371721</t>
   </si>
   <si>
@@ -352,15 +358,15 @@
     <t>721907</t>
   </si>
   <si>
-    <t>900309</t>
-  </si>
-  <si>
     <t>743304</t>
   </si>
   <si>
     <t>567574</t>
   </si>
   <si>
+    <t>528180</t>
+  </si>
+  <si>
     <t>206074</t>
   </si>
   <si>
@@ -376,7 +382,7 @@
     <t>946785</t>
   </si>
   <si>
-    <t>793271</t>
+    <t>934745</t>
   </si>
   <si>
     <t>212105</t>
@@ -385,7 +391,7 @@
     <t>969447</t>
   </si>
   <si>
-    <t>353604</t>
+    <t>112640</t>
   </si>
   <si>
     <t>278415</t>
@@ -394,9 +400,6 @@
     <t>352797</t>
   </si>
   <si>
-    <t>416384</t>
-  </si>
-  <si>
     <t>047730</t>
   </si>
   <si>
@@ -430,24 +433,30 @@
     <t>169639</t>
   </si>
   <si>
-    <t>298748</t>
-  </si>
-  <si>
     <t>812058</t>
   </si>
   <si>
     <t>072604</t>
   </si>
   <si>
+    <t>826129</t>
+  </si>
+  <si>
     <t>681805</t>
   </si>
   <si>
+    <t>505868</t>
+  </si>
+  <si>
     <t>468380</t>
   </si>
   <si>
     <t>954978</t>
   </si>
   <si>
+    <t>006931</t>
+  </si>
+  <si>
     <t>385430</t>
   </si>
   <si>
@@ -472,15 +481,15 @@
     <t>089576</t>
   </si>
   <si>
-    <t>409539</t>
-  </si>
-  <si>
     <t>204255</t>
   </si>
   <si>
     <t>711191</t>
   </si>
   <si>
+    <t>922284</t>
+  </si>
+  <si>
     <t>393352</t>
   </si>
   <si>
@@ -514,6 +523,9 @@
     <t>969831</t>
   </si>
   <si>
+    <t>201069</t>
+  </si>
+  <si>
     <t>909882</t>
   </si>
   <si>
@@ -550,6 +562,9 @@
     <t>960358</t>
   </si>
   <si>
+    <t>164365</t>
+  </si>
+  <si>
     <t>262100</t>
   </si>
   <si>
@@ -559,10 +574,7 @@
     <t>831899</t>
   </si>
   <si>
-    <t>263856</t>
-  </si>
-  <si>
-    <t>693559</t>
+    <t>065068</t>
   </si>
   <si>
     <t>948389</t>
@@ -571,9 +583,6 @@
     <t>817714</t>
   </si>
   <si>
-    <t>952926</t>
-  </si>
-  <si>
     <t>379499</t>
   </si>
   <si>
@@ -592,9 +601,6 @@
     <t>676658</t>
   </si>
   <si>
-    <t>873354</t>
-  </si>
-  <si>
     <t>436654</t>
   </si>
   <si>
@@ -610,24 +616,33 @@
     <t>040225</t>
   </si>
   <si>
-    <t>710345</t>
+    <t>284247</t>
   </si>
   <si>
     <t>823358</t>
   </si>
   <si>
-    <t>435167</t>
+    <t>946623</t>
+  </si>
+  <si>
+    <t>711230</t>
   </si>
   <si>
     <t>040653</t>
   </si>
   <si>
-    <t>046026</t>
+    <t>739006</t>
+  </si>
+  <si>
+    <t>144971</t>
   </si>
   <si>
     <t>848125</t>
   </si>
   <si>
+    <t>152148</t>
+  </si>
+  <si>
     <t>008327</t>
   </si>
   <si>
@@ -646,18 +661,12 @@
     <t>994993</t>
   </si>
   <si>
-    <t>415764</t>
-  </si>
-  <si>
     <t>921152</t>
   </si>
   <si>
     <t>666886</t>
   </si>
   <si>
-    <t>773482</t>
-  </si>
-  <si>
     <t>184440</t>
   </si>
   <si>
@@ -667,9 +676,6 @@
     <t>769514</t>
   </si>
   <si>
-    <t>490662</t>
-  </si>
-  <si>
     <t>242407</t>
   </si>
   <si>
@@ -697,6 +703,9 @@
     <t>626309</t>
   </si>
   <si>
+    <t>388514</t>
+  </si>
+  <si>
     <t>337467</t>
   </si>
   <si>
@@ -709,6 +718,9 @@
     <t>967880</t>
   </si>
   <si>
+    <t>959714</t>
+  </si>
+  <si>
     <t>882848</t>
   </si>
   <si>
@@ -757,9 +769,6 @@
     <t>866987</t>
   </si>
   <si>
-    <t>686902</t>
-  </si>
-  <si>
     <t>724271</t>
   </si>
   <si>
@@ -799,15 +808,18 @@
     <t>968025</t>
   </si>
   <si>
+    <t>675543</t>
+  </si>
+  <si>
+    <t>864197</t>
+  </si>
+  <si>
     <t>817354</t>
   </si>
   <si>
     <t>814151</t>
   </si>
   <si>
-    <t>200803</t>
-  </si>
-  <si>
     <t>623457</t>
   </si>
   <si>
@@ -820,12 +832,18 @@
     <t>596941</t>
   </si>
   <si>
+    <t>124247</t>
+  </si>
+  <si>
+    <t>640773</t>
+  </si>
+  <si>
+    <t>129780</t>
+  </si>
+  <si>
     <t>443196</t>
   </si>
   <si>
-    <t>710250</t>
-  </si>
-  <si>
     <t>158437</t>
   </si>
   <si>
@@ -865,27 +883,27 @@
     <t>442086</t>
   </si>
   <si>
-    <t>763422</t>
+    <t>633855</t>
   </si>
   <si>
     <t>477308</t>
   </si>
   <si>
+    <t>780219</t>
+  </si>
+  <si>
     <t>171043</t>
   </si>
   <si>
     <t>860113</t>
   </si>
   <si>
-    <t>018347</t>
+    <t>648064</t>
   </si>
   <si>
     <t>920275</t>
   </si>
   <si>
-    <t>744654</t>
-  </si>
-  <si>
     <t>778586</t>
   </si>
   <si>
@@ -895,10 +913,10 @@
     <t>002210</t>
   </si>
   <si>
+    <t>active</t>
+  </si>
+  <si>
     <t>paused</t>
-  </si>
-  <si>
-    <t>active</t>
   </si>
 </sst>
 </file>
@@ -1256,7 +1274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E289"/>
+  <dimension ref="A1:E295"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1281,16 +1299,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>414700</v>
+        <v>318500</v>
       </c>
       <c r="C2">
-        <v>353267</v>
+        <v>281707</v>
       </c>
       <c r="D2">
-        <v>399346</v>
+        <v>318451</v>
       </c>
       <c r="E2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1298,16 +1316,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>207000</v>
+        <v>414400</v>
       </c>
       <c r="C3">
-        <v>183169</v>
+        <v>366561</v>
       </c>
       <c r="D3">
-        <v>207061</v>
+        <v>414373</v>
       </c>
       <c r="E3" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1315,16 +1333,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>228500</v>
+        <v>367961</v>
       </c>
       <c r="C4">
-        <v>202225</v>
+        <v>461101</v>
       </c>
       <c r="D4">
-        <v>228602</v>
+        <v>521245</v>
       </c>
       <c r="E4" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1332,16 +1350,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>72104</v>
+        <v>197600</v>
       </c>
       <c r="C5">
-        <v>232229</v>
+        <v>174843</v>
       </c>
       <c r="D5">
-        <v>262520</v>
+        <v>197649</v>
       </c>
       <c r="E5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1349,16 +1367,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>230100</v>
+        <v>218200</v>
       </c>
       <c r="C6">
-        <v>200893</v>
+        <v>193033</v>
       </c>
       <c r="D6">
-        <v>227097</v>
+        <v>218211</v>
       </c>
       <c r="E6" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1366,16 +1384,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>325900</v>
+        <v>75990</v>
       </c>
       <c r="C7">
-        <v>288306</v>
+        <v>215340</v>
       </c>
       <c r="D7">
-        <v>325911</v>
+        <v>243428</v>
       </c>
       <c r="E7" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1383,16 +1401,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>131617</v>
+        <v>206534</v>
       </c>
       <c r="C8">
-        <v>514065</v>
+        <v>191762</v>
       </c>
       <c r="D8">
-        <v>581117</v>
+        <v>216774</v>
       </c>
       <c r="E8" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1400,16 +1418,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>654200</v>
+        <v>263400</v>
       </c>
       <c r="C9">
-        <v>538256</v>
+        <v>224821</v>
       </c>
       <c r="D9">
-        <v>608464</v>
+        <v>254146</v>
       </c>
       <c r="E9" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1417,16 +1435,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>147223</v>
+        <v>214300</v>
       </c>
       <c r="C10">
-        <v>481990</v>
+        <v>189576</v>
       </c>
       <c r="D10">
-        <v>544858</v>
+        <v>214303</v>
       </c>
       <c r="E10" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1434,16 +1452,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>523900</v>
+        <v>263000</v>
       </c>
       <c r="C11">
-        <v>556693</v>
+        <v>232491</v>
       </c>
       <c r="D11">
-        <v>629305</v>
+        <v>262816</v>
       </c>
       <c r="E11" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1451,16 +1469,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>372645</v>
+        <v>206834</v>
       </c>
       <c r="C12">
-        <v>332753</v>
+        <v>192149</v>
       </c>
       <c r="D12">
-        <v>376155</v>
+        <v>217212</v>
       </c>
       <c r="E12" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1468,16 +1486,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>106132</v>
+        <v>280400</v>
       </c>
       <c r="C13">
-        <v>416698</v>
+        <v>248117</v>
       </c>
       <c r="D13">
-        <v>471050</v>
+        <v>280480</v>
       </c>
       <c r="E13" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1485,16 +1503,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>144953</v>
+        <v>138709</v>
       </c>
       <c r="C14">
-        <v>432640</v>
+        <v>547377</v>
       </c>
       <c r="D14">
-        <v>489072</v>
+        <v>618774</v>
       </c>
       <c r="E14" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1502,16 +1520,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>268300</v>
+        <v>689452</v>
       </c>
       <c r="C15">
-        <v>237941</v>
+        <v>650159</v>
       </c>
       <c r="D15">
-        <v>268976</v>
+        <v>734963</v>
       </c>
       <c r="E15" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1519,16 +1537,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>231600</v>
+        <v>112388</v>
       </c>
       <c r="C16">
-        <v>204900</v>
+        <v>432378</v>
       </c>
       <c r="D16">
-        <v>231626</v>
+        <v>488775</v>
       </c>
       <c r="E16" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1536,16 +1554,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>74709</v>
+        <v>132184</v>
       </c>
       <c r="C17">
-        <v>206693</v>
+        <v>448920</v>
       </c>
       <c r="D17">
-        <v>233653</v>
+        <v>507475</v>
       </c>
       <c r="E17" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1553,16 +1571,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>233900</v>
+        <v>79590</v>
       </c>
       <c r="C18">
-        <v>206966</v>
+        <v>245126</v>
       </c>
       <c r="D18">
-        <v>233962</v>
+        <v>277100</v>
       </c>
       <c r="E18" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1570,16 +1588,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>314123</v>
+        <v>210500</v>
       </c>
       <c r="C19">
-        <v>233392</v>
+        <v>195587</v>
       </c>
       <c r="D19">
-        <v>263835</v>
+        <v>221098</v>
       </c>
       <c r="E19" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1587,16 +1605,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>240400</v>
+        <v>235900</v>
       </c>
       <c r="C20">
-        <v>212668</v>
+        <v>212936</v>
       </c>
       <c r="D20">
-        <v>240407</v>
+        <v>240710</v>
       </c>
       <c r="E20" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1604,16 +1622,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>264900</v>
+        <v>223300</v>
       </c>
       <c r="C21">
-        <v>234346</v>
+        <v>197558</v>
       </c>
       <c r="D21">
-        <v>264913</v>
+        <v>223327</v>
       </c>
       <c r="E21" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1621,16 +1639,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>254500</v>
+        <v>89407</v>
       </c>
       <c r="C22">
-        <v>225155</v>
+        <v>240441</v>
       </c>
       <c r="D22">
-        <v>254523</v>
+        <v>271802</v>
       </c>
       <c r="E22" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1638,16 +1656,16 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>290200</v>
+        <v>138378</v>
       </c>
       <c r="C23">
-        <v>256715</v>
+        <v>352848</v>
       </c>
       <c r="D23">
-        <v>290200</v>
+        <v>398872</v>
       </c>
       <c r="E23" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1655,16 +1673,16 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>263300</v>
+        <v>229500</v>
       </c>
       <c r="C24">
-        <v>232928</v>
+        <v>203001</v>
       </c>
       <c r="D24">
-        <v>263310</v>
+        <v>229479</v>
       </c>
       <c r="E24" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1672,16 +1690,16 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>308200</v>
+        <v>272900</v>
       </c>
       <c r="C25">
-        <v>272677</v>
+        <v>241424</v>
       </c>
       <c r="D25">
-        <v>308244</v>
+        <v>272914</v>
       </c>
       <c r="E25" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1689,16 +1707,16 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>257500</v>
+        <v>231400</v>
       </c>
       <c r="C26">
-        <v>455638</v>
+        <v>214921</v>
       </c>
       <c r="D26">
-        <v>515069</v>
+        <v>242954</v>
       </c>
       <c r="E26" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1706,16 +1724,16 @@
         <v>30</v>
       </c>
       <c r="B27">
-        <v>525700</v>
+        <v>305837</v>
       </c>
       <c r="C27">
-        <v>465087</v>
+        <v>264468</v>
       </c>
       <c r="D27">
-        <v>525750</v>
+        <v>298964</v>
       </c>
       <c r="E27" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1723,16 +1741,16 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>320706</v>
+        <v>239324</v>
       </c>
       <c r="C28">
-        <v>312144</v>
+        <v>222340</v>
       </c>
       <c r="D28">
-        <v>352858</v>
+        <v>251341</v>
       </c>
       <c r="E28" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1740,16 +1758,16 @@
         <v>32</v>
       </c>
       <c r="B29">
-        <v>285400</v>
+        <v>317600</v>
       </c>
       <c r="C29">
-        <v>252490</v>
+        <v>280912</v>
       </c>
       <c r="D29">
-        <v>285424</v>
+        <v>317553</v>
       </c>
       <c r="E29" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1757,16 +1775,16 @@
         <v>33</v>
       </c>
       <c r="B30">
-        <v>313400</v>
+        <v>515607</v>
       </c>
       <c r="C30">
-        <v>277309</v>
+        <v>380637</v>
       </c>
       <c r="D30">
-        <v>313480</v>
+        <v>430285</v>
       </c>
       <c r="E30" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1774,16 +1792,16 @@
         <v>34</v>
       </c>
       <c r="B31">
-        <v>528600</v>
+        <v>528833</v>
       </c>
       <c r="C31">
-        <v>467662</v>
+        <v>388530</v>
       </c>
       <c r="D31">
-        <v>528662</v>
+        <v>439208</v>
       </c>
       <c r="E31" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1791,16 +1809,16 @@
         <v>35</v>
       </c>
       <c r="B32">
-        <v>174097</v>
+        <v>337987</v>
       </c>
       <c r="C32">
-        <v>403628</v>
+        <v>321571</v>
       </c>
       <c r="D32">
-        <v>456276</v>
+        <v>363515</v>
       </c>
       <c r="E32" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1808,16 +1826,16 @@
         <v>36</v>
       </c>
       <c r="B33">
-        <v>223116</v>
+        <v>259400</v>
       </c>
       <c r="C33">
-        <v>610066</v>
+        <v>241013</v>
       </c>
       <c r="D33">
-        <v>689640</v>
+        <v>272450</v>
       </c>
       <c r="E33" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1825,16 +1843,16 @@
         <v>37</v>
       </c>
       <c r="B34">
-        <v>540400</v>
+        <v>328305</v>
       </c>
       <c r="C34">
-        <v>478110</v>
+        <v>285684</v>
       </c>
       <c r="D34">
-        <v>540472</v>
+        <v>322947</v>
       </c>
       <c r="E34" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1842,16 +1860,16 @@
         <v>38</v>
       </c>
       <c r="B35">
-        <v>720281</v>
+        <v>557083</v>
       </c>
       <c r="C35">
-        <v>672518</v>
+        <v>390682</v>
       </c>
       <c r="D35">
-        <v>760238</v>
+        <v>441640</v>
       </c>
       <c r="E35" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1859,16 +1877,16 @@
         <v>39</v>
       </c>
       <c r="B36">
-        <v>392400</v>
+        <v>596012</v>
       </c>
       <c r="C36">
-        <v>347041</v>
+        <v>537902</v>
       </c>
       <c r="D36">
-        <v>392308</v>
+        <v>608063</v>
       </c>
       <c r="E36" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1876,16 +1894,16 @@
         <v>40</v>
       </c>
       <c r="B37">
-        <v>699389</v>
+        <v>702300</v>
       </c>
       <c r="C37">
-        <v>731787</v>
+        <v>621256</v>
       </c>
       <c r="D37">
-        <v>827237</v>
+        <v>702289</v>
       </c>
       <c r="E37" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1893,16 +1911,16 @@
         <v>41</v>
       </c>
       <c r="B38">
-        <v>735612</v>
+        <v>390900</v>
       </c>
       <c r="C38">
-        <v>695500</v>
+        <v>345791</v>
       </c>
       <c r="D38">
-        <v>786217</v>
+        <v>390894</v>
       </c>
       <c r="E38" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1910,16 +1928,16 @@
         <v>42</v>
       </c>
       <c r="B39">
-        <v>109253</v>
+        <v>333356</v>
       </c>
       <c r="C39">
-        <v>367060</v>
+        <v>717342</v>
       </c>
       <c r="D39">
-        <v>414938</v>
+        <v>810908</v>
       </c>
       <c r="E39" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1927,16 +1945,16 @@
         <v>43</v>
       </c>
       <c r="B40">
-        <v>417100</v>
+        <v>374400</v>
       </c>
       <c r="C40">
-        <v>369035</v>
+        <v>331267</v>
       </c>
       <c r="D40">
-        <v>417170</v>
+        <v>374475</v>
       </c>
       <c r="E40" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1944,16 +1962,16 @@
         <v>44</v>
       </c>
       <c r="B41">
-        <v>261000</v>
+        <v>737076</v>
       </c>
       <c r="C41">
-        <v>230929</v>
+        <v>775989</v>
       </c>
       <c r="D41">
-        <v>261050</v>
+        <v>877205</v>
       </c>
       <c r="E41" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1961,16 +1979,16 @@
         <v>45</v>
       </c>
       <c r="B42">
-        <v>422800</v>
+        <v>775250</v>
       </c>
       <c r="C42">
-        <v>374031</v>
+        <v>741440</v>
       </c>
       <c r="D42">
-        <v>422818</v>
+        <v>838149</v>
       </c>
       <c r="E42" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1978,16 +1996,16 @@
         <v>46</v>
       </c>
       <c r="B43">
-        <v>263000</v>
+        <v>436000</v>
       </c>
       <c r="C43">
-        <v>232697</v>
+        <v>397280</v>
       </c>
       <c r="D43">
-        <v>263049</v>
+        <v>449099</v>
       </c>
       <c r="E43" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1995,16 +2013,16 @@
         <v>47</v>
       </c>
       <c r="B44">
-        <v>97493</v>
+        <v>438400</v>
       </c>
       <c r="C44">
-        <v>303521</v>
+        <v>399417</v>
       </c>
       <c r="D44">
-        <v>343111</v>
+        <v>451515</v>
       </c>
       <c r="E44" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2012,16 +2030,16 @@
         <v>48</v>
       </c>
       <c r="B45">
-        <v>396900</v>
+        <v>237300</v>
       </c>
       <c r="C45">
-        <v>351123</v>
+        <v>220432</v>
       </c>
       <c r="D45">
-        <v>396922</v>
+        <v>249184</v>
       </c>
       <c r="E45" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2029,16 +2047,16 @@
         <v>49</v>
       </c>
       <c r="B46">
-        <v>480400</v>
+        <v>435600</v>
       </c>
       <c r="C46">
-        <v>425012</v>
+        <v>323860</v>
       </c>
       <c r="D46">
-        <v>480448</v>
+        <v>366102</v>
       </c>
       <c r="E46" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2046,16 +2064,16 @@
         <v>50</v>
       </c>
       <c r="B47">
-        <v>433800</v>
+        <v>239200</v>
       </c>
       <c r="C47">
-        <v>383763</v>
+        <v>222120</v>
       </c>
       <c r="D47">
-        <v>433819</v>
+        <v>251092</v>
       </c>
       <c r="E47" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2063,16 +2081,16 @@
         <v>51</v>
       </c>
       <c r="B48">
-        <v>236600</v>
+        <v>408900</v>
       </c>
       <c r="C48">
-        <v>209312</v>
+        <v>380031</v>
       </c>
       <c r="D48">
-        <v>236613</v>
+        <v>429600</v>
       </c>
       <c r="E48" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2080,16 +2098,16 @@
         <v>52</v>
       </c>
       <c r="B49">
-        <v>794074</v>
+        <v>499800</v>
       </c>
       <c r="C49">
-        <v>567604</v>
+        <v>455404</v>
       </c>
       <c r="D49">
-        <v>641639</v>
+        <v>514805</v>
       </c>
       <c r="E49" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2097,16 +2115,16 @@
         <v>53</v>
       </c>
       <c r="B50">
-        <v>292800</v>
+        <v>451300</v>
       </c>
       <c r="C50">
-        <v>259087</v>
+        <v>411206</v>
       </c>
       <c r="D50">
-        <v>292881</v>
+        <v>464841</v>
       </c>
       <c r="E50" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2114,16 +2132,16 @@
         <v>54</v>
       </c>
       <c r="B51">
-        <v>451300</v>
+        <v>215000</v>
       </c>
       <c r="C51">
-        <v>399185</v>
+        <v>199798</v>
       </c>
       <c r="D51">
-        <v>451253</v>
+        <v>225858</v>
       </c>
       <c r="E51" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2131,16 +2149,16 @@
         <v>55</v>
       </c>
       <c r="B52">
-        <v>291700</v>
+        <v>836863</v>
       </c>
       <c r="C52">
-        <v>258050</v>
+        <v>527312</v>
       </c>
       <c r="D52">
-        <v>291709</v>
+        <v>596092</v>
       </c>
       <c r="E52" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2148,16 +2166,16 @@
         <v>56</v>
       </c>
       <c r="B53">
-        <v>409000</v>
+        <v>464900</v>
       </c>
       <c r="C53">
-        <v>361813</v>
+        <v>432050</v>
       </c>
       <c r="D53">
-        <v>409007</v>
+        <v>488404</v>
       </c>
       <c r="E53" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2165,16 +2183,16 @@
         <v>57</v>
       </c>
       <c r="B54">
-        <v>408400</v>
+        <v>278500</v>
       </c>
       <c r="C54">
-        <v>361279</v>
+        <v>246321</v>
       </c>
       <c r="D54">
-        <v>408403</v>
+        <v>278450</v>
       </c>
       <c r="E54" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2182,16 +2200,16 @@
         <v>58</v>
       </c>
       <c r="B55">
-        <v>464300</v>
+        <v>431038</v>
       </c>
       <c r="C55">
-        <v>410729</v>
+        <v>391601</v>
       </c>
       <c r="D55">
-        <v>464302</v>
+        <v>442679</v>
       </c>
       <c r="E55" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2199,16 +2217,16 @@
         <v>59</v>
       </c>
       <c r="B56">
-        <v>522000</v>
+        <v>422356</v>
       </c>
       <c r="C56">
-        <v>503228</v>
+        <v>391023</v>
       </c>
       <c r="D56">
-        <v>568867</v>
+        <v>442026</v>
       </c>
       <c r="E56" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2216,16 +2234,16 @@
         <v>60</v>
       </c>
       <c r="B57">
-        <v>281700</v>
+        <v>483000</v>
       </c>
       <c r="C57">
-        <v>252537</v>
+        <v>440100</v>
       </c>
       <c r="D57">
-        <v>285477</v>
+        <v>497504</v>
       </c>
       <c r="E57" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2233,16 +2251,16 @@
         <v>61</v>
       </c>
       <c r="B58">
-        <v>552100</v>
+        <v>550127</v>
       </c>
       <c r="C58">
-        <v>418423</v>
+        <v>544658</v>
       </c>
       <c r="D58">
-        <v>473000</v>
+        <v>615701</v>
       </c>
       <c r="E58" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2250,16 +2268,16 @@
         <v>62</v>
       </c>
       <c r="B59">
-        <v>541380</v>
+        <v>272500</v>
       </c>
       <c r="C59">
-        <v>524781</v>
+        <v>241058</v>
       </c>
       <c r="D59">
-        <v>593231</v>
+        <v>272501</v>
       </c>
       <c r="E59" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2267,16 +2285,16 @@
         <v>63</v>
       </c>
       <c r="B60">
-        <v>515600</v>
+        <v>511900</v>
       </c>
       <c r="C60">
-        <v>456133</v>
+        <v>452871</v>
       </c>
       <c r="D60">
-        <v>515629</v>
+        <v>511942</v>
       </c>
       <c r="E60" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2284,16 +2302,16 @@
         <v>64</v>
       </c>
       <c r="B61">
-        <v>334700</v>
+        <v>599700</v>
       </c>
       <c r="C61">
-        <v>296135</v>
+        <v>433359</v>
       </c>
       <c r="D61">
-        <v>334762</v>
+        <v>489885</v>
       </c>
       <c r="E61" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2301,16 +2319,16 @@
         <v>65</v>
       </c>
       <c r="B62">
-        <v>428400</v>
+        <v>536400</v>
       </c>
       <c r="C62">
-        <v>379034</v>
+        <v>488751</v>
       </c>
       <c r="D62">
-        <v>428473</v>
+        <v>552501</v>
       </c>
       <c r="E62" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2318,16 +2336,16 @@
         <v>66</v>
       </c>
       <c r="B63">
-        <v>442000</v>
+        <v>352735</v>
       </c>
       <c r="C63">
-        <v>391016</v>
+        <v>282674</v>
       </c>
       <c r="D63">
-        <v>442018</v>
+        <v>319545</v>
       </c>
       <c r="E63" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2335,16 +2353,16 @@
         <v>67</v>
       </c>
       <c r="B64">
-        <v>547800</v>
+        <v>456121</v>
       </c>
       <c r="C64">
-        <v>484645</v>
+        <v>328192</v>
       </c>
       <c r="D64">
-        <v>547860</v>
+        <v>370999</v>
       </c>
       <c r="E64" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2352,16 +2370,16 @@
         <v>68</v>
       </c>
       <c r="B65">
-        <v>501500</v>
+        <v>459000</v>
       </c>
       <c r="C65">
-        <v>443714</v>
+        <v>363259</v>
       </c>
       <c r="D65">
-        <v>501590</v>
+        <v>410641</v>
       </c>
       <c r="E65" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2369,16 +2387,16 @@
         <v>69</v>
       </c>
       <c r="B66">
-        <v>633800</v>
+        <v>575700</v>
       </c>
       <c r="C66">
-        <v>560713</v>
+        <v>524545</v>
       </c>
       <c r="D66">
-        <v>633850</v>
+        <v>592964</v>
       </c>
       <c r="E66" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2386,16 +2404,16 @@
         <v>70</v>
       </c>
       <c r="B67">
-        <v>525600</v>
+        <v>521800</v>
       </c>
       <c r="C67">
-        <v>412745</v>
+        <v>475444</v>
       </c>
       <c r="D67">
-        <v>466581</v>
+        <v>537459</v>
       </c>
       <c r="E67" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2403,16 +2421,16 @@
         <v>71</v>
       </c>
       <c r="B68">
-        <v>556100</v>
+        <v>639000</v>
       </c>
       <c r="C68">
-        <v>485239</v>
+        <v>600809</v>
       </c>
       <c r="D68">
-        <v>548531</v>
+        <v>679176</v>
       </c>
       <c r="E68" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2420,16 +2438,16 @@
         <v>72</v>
       </c>
       <c r="B69">
-        <v>537600</v>
+        <v>564822</v>
       </c>
       <c r="C69">
-        <v>475581</v>
+        <v>405714</v>
       </c>
       <c r="D69">
-        <v>537613</v>
+        <v>458634</v>
       </c>
       <c r="E69" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2437,16 +2455,16 @@
         <v>73</v>
       </c>
       <c r="B70">
-        <v>535100</v>
+        <v>566568</v>
       </c>
       <c r="C70">
-        <v>473394</v>
+        <v>509589</v>
       </c>
       <c r="D70">
-        <v>535141</v>
+        <v>576058</v>
       </c>
       <c r="E70" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2454,16 +2472,16 @@
         <v>74</v>
       </c>
       <c r="B71">
-        <v>557100</v>
+        <v>562300</v>
       </c>
       <c r="C71">
-        <v>492875</v>
+        <v>512368</v>
       </c>
       <c r="D71">
-        <v>557163</v>
+        <v>579199</v>
       </c>
       <c r="E71" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2471,16 +2489,16 @@
         <v>75</v>
       </c>
       <c r="B72">
-        <v>722500</v>
+        <v>579600</v>
       </c>
       <c r="C72">
-        <v>639154</v>
+        <v>528120</v>
       </c>
       <c r="D72">
-        <v>722521</v>
+        <v>597005</v>
       </c>
       <c r="E72" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2488,16 +2506,16 @@
         <v>76</v>
       </c>
       <c r="B73">
-        <v>619300</v>
+        <v>744065</v>
       </c>
       <c r="C73">
-        <v>547850</v>
+        <v>691774</v>
       </c>
       <c r="D73">
-        <v>619309</v>
+        <v>782006</v>
       </c>
       <c r="E73" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2505,16 +2523,16 @@
         <v>77</v>
       </c>
       <c r="B74">
-        <v>556101</v>
+        <v>637799</v>
       </c>
       <c r="C74">
-        <v>560669</v>
+        <v>592954</v>
       </c>
       <c r="D74">
-        <v>633799</v>
+        <v>670295</v>
       </c>
       <c r="E74" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2522,16 +2540,16 @@
         <v>78</v>
       </c>
       <c r="B75">
-        <v>562200</v>
+        <v>633900</v>
       </c>
       <c r="C75">
-        <v>478901</v>
+        <v>600762</v>
       </c>
       <c r="D75">
-        <v>541367</v>
+        <v>679122</v>
       </c>
       <c r="E75" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2539,16 +2557,16 @@
         <v>79</v>
       </c>
       <c r="B76">
-        <v>555700</v>
+        <v>583900</v>
       </c>
       <c r="C76">
-        <v>491576</v>
+        <v>532046</v>
       </c>
       <c r="D76">
-        <v>555695</v>
+        <v>601444</v>
       </c>
       <c r="E76" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2556,16 +2574,16 @@
         <v>80</v>
       </c>
       <c r="B77">
-        <v>721000</v>
+        <v>799800</v>
       </c>
       <c r="C77">
-        <v>629572</v>
+        <v>528769</v>
       </c>
       <c r="D77">
-        <v>711690</v>
+        <v>597738</v>
       </c>
       <c r="E77" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2573,16 +2591,16 @@
         <v>81</v>
       </c>
       <c r="B78">
-        <v>490300</v>
+        <v>387300</v>
       </c>
       <c r="C78">
-        <v>451894</v>
+        <v>342579</v>
       </c>
       <c r="D78">
-        <v>510836</v>
+        <v>387263</v>
       </c>
       <c r="E78" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2590,16 +2608,16 @@
         <v>82</v>
       </c>
       <c r="B79">
-        <v>764600</v>
+        <v>536800</v>
       </c>
       <c r="C79">
-        <v>625171</v>
+        <v>489097</v>
       </c>
       <c r="D79">
-        <v>706715</v>
+        <v>552893</v>
       </c>
       <c r="E79" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2607,16 +2625,16 @@
         <v>83</v>
       </c>
       <c r="B80">
-        <v>128998</v>
+        <v>742600</v>
       </c>
       <c r="C80">
-        <v>476359</v>
+        <v>676640</v>
       </c>
       <c r="D80">
-        <v>538493</v>
+        <v>764898</v>
       </c>
       <c r="E80" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2624,16 +2642,16 @@
         <v>84</v>
       </c>
       <c r="B81">
-        <v>438500</v>
+        <v>173616</v>
       </c>
       <c r="C81">
-        <v>387951</v>
+        <v>515577</v>
       </c>
       <c r="D81">
-        <v>438554</v>
+        <v>582827</v>
       </c>
       <c r="E81" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2641,16 +2659,16 @@
         <v>85</v>
       </c>
       <c r="B82">
-        <v>552200</v>
+        <v>631200</v>
       </c>
       <c r="C82">
-        <v>488401</v>
+        <v>586581</v>
       </c>
       <c r="D82">
-        <v>552105</v>
+        <v>663092</v>
       </c>
       <c r="E82" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2658,16 +2676,16 @@
         <v>86</v>
       </c>
       <c r="B83">
-        <v>701900</v>
+        <v>775000</v>
       </c>
       <c r="C83">
-        <v>612908</v>
+        <v>706108</v>
       </c>
       <c r="D83">
-        <v>692853</v>
+        <v>798209</v>
       </c>
       <c r="E83" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2675,16 +2693,16 @@
         <v>87</v>
       </c>
       <c r="B84">
-        <v>860900</v>
+        <v>580200</v>
       </c>
       <c r="C84">
-        <v>751659</v>
+        <v>528610</v>
       </c>
       <c r="D84">
-        <v>849701</v>
+        <v>597559</v>
       </c>
       <c r="E84" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2692,16 +2710,16 @@
         <v>88</v>
       </c>
       <c r="B85">
-        <v>687700</v>
+        <v>728000</v>
       </c>
       <c r="C85">
-        <v>637448</v>
+        <v>663368</v>
       </c>
       <c r="D85">
-        <v>720594</v>
+        <v>749895</v>
       </c>
       <c r="E85" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2709,16 +2727,16 @@
         <v>89</v>
       </c>
       <c r="B86">
-        <v>653939</v>
+        <v>875124</v>
       </c>
       <c r="C86">
-        <v>662555</v>
+        <v>813542</v>
       </c>
       <c r="D86">
-        <v>748976</v>
+        <v>919656</v>
       </c>
       <c r="E86" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2726,16 +2744,16 @@
         <v>90</v>
       </c>
       <c r="B87">
-        <v>649000</v>
+        <v>757200</v>
       </c>
       <c r="C87">
-        <v>574190</v>
+        <v>689928</v>
       </c>
       <c r="D87">
-        <v>649085</v>
+        <v>779919</v>
       </c>
       <c r="E87" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2743,16 +2761,16 @@
         <v>91</v>
       </c>
       <c r="B88">
-        <v>450700</v>
+        <v>1073561</v>
       </c>
       <c r="C88">
-        <v>387930</v>
+        <v>998039</v>
       </c>
       <c r="D88">
-        <v>438529</v>
+        <v>1128218</v>
       </c>
       <c r="E88" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2760,16 +2778,16 @@
         <v>92</v>
       </c>
       <c r="B89">
-        <v>454800</v>
+        <v>689176</v>
       </c>
       <c r="C89">
-        <v>402358</v>
+        <v>687487</v>
       </c>
       <c r="D89">
-        <v>454839</v>
+        <v>777159</v>
       </c>
       <c r="E89" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2777,16 +2795,16 @@
         <v>93</v>
       </c>
       <c r="B90">
-        <v>295600</v>
+        <v>260000</v>
       </c>
       <c r="C90">
-        <v>261495</v>
+        <v>241620</v>
       </c>
       <c r="D90">
-        <v>295603</v>
+        <v>273136</v>
       </c>
       <c r="E90" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2794,16 +2812,16 @@
         <v>94</v>
       </c>
       <c r="B91">
-        <v>387900</v>
+        <v>668700</v>
       </c>
       <c r="C91">
-        <v>343164</v>
+        <v>621463</v>
       </c>
       <c r="D91">
-        <v>387924</v>
+        <v>702523</v>
       </c>
       <c r="E91" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2811,16 +2829,16 @@
         <v>95</v>
       </c>
       <c r="B92">
-        <v>220462</v>
+        <v>476431</v>
       </c>
       <c r="C92">
-        <v>681016</v>
+        <v>435483</v>
       </c>
       <c r="D92">
-        <v>769845</v>
+        <v>492286</v>
       </c>
       <c r="E92" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2828,16 +2846,16 @@
         <v>96</v>
       </c>
       <c r="B93">
-        <v>578994</v>
+        <v>311528</v>
       </c>
       <c r="C93">
-        <v>369862</v>
+        <v>249609</v>
       </c>
       <c r="D93">
-        <v>418105</v>
+        <v>282167</v>
       </c>
       <c r="E93" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2845,16 +2863,16 @@
         <v>97</v>
       </c>
       <c r="B94">
-        <v>585600</v>
+        <v>407600</v>
       </c>
       <c r="C94">
-        <v>518050</v>
+        <v>371416</v>
       </c>
       <c r="D94">
-        <v>585622</v>
+        <v>419861</v>
       </c>
       <c r="E94" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2862,16 +2880,16 @@
         <v>98</v>
       </c>
       <c r="B95">
-        <v>314700</v>
+        <v>808900</v>
       </c>
       <c r="C95">
-        <v>278439</v>
+        <v>737084</v>
       </c>
       <c r="D95">
-        <v>314757</v>
+        <v>833225</v>
       </c>
       <c r="E95" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2879,16 +2897,16 @@
         <v>99</v>
       </c>
       <c r="B96">
-        <v>484900</v>
+        <v>610193</v>
       </c>
       <c r="C96">
-        <v>428946</v>
+        <v>320250</v>
       </c>
       <c r="D96">
-        <v>484896</v>
+        <v>362022</v>
       </c>
       <c r="E96" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2896,16 +2914,16 @@
         <v>100</v>
       </c>
       <c r="B97">
-        <v>313500</v>
+        <v>615400</v>
       </c>
       <c r="C97">
-        <v>277369</v>
+        <v>560701</v>
       </c>
       <c r="D97">
-        <v>313547</v>
+        <v>633836</v>
       </c>
       <c r="E97" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2913,16 +2931,16 @@
         <v>101</v>
       </c>
       <c r="B98">
-        <v>449842</v>
+        <v>300500</v>
       </c>
       <c r="C98">
-        <v>315603</v>
+        <v>265782</v>
       </c>
       <c r="D98">
-        <v>356768</v>
+        <v>300450</v>
       </c>
       <c r="E98" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2930,16 +2948,16 @@
         <v>102</v>
       </c>
       <c r="B99">
-        <v>308400</v>
+        <v>499500</v>
       </c>
       <c r="C99">
-        <v>272858</v>
+        <v>464261</v>
       </c>
       <c r="D99">
-        <v>308449</v>
+        <v>524816</v>
       </c>
       <c r="E99" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2947,16 +2965,16 @@
         <v>103</v>
       </c>
       <c r="B100">
-        <v>408000</v>
+        <v>285000</v>
       </c>
       <c r="C100">
-        <v>374084</v>
+        <v>264761</v>
       </c>
       <c r="D100">
-        <v>422878</v>
+        <v>299295</v>
       </c>
       <c r="E100" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2964,16 +2982,16 @@
         <v>104</v>
       </c>
       <c r="B101">
-        <v>526400</v>
+        <v>294400</v>
       </c>
       <c r="C101">
-        <v>374084</v>
+        <v>260456</v>
       </c>
       <c r="D101">
-        <v>422878</v>
+        <v>294428</v>
       </c>
       <c r="E101" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2981,16 +2999,16 @@
         <v>105</v>
       </c>
       <c r="B102">
-        <v>623700</v>
+        <v>588274</v>
       </c>
       <c r="C102">
-        <v>517417</v>
+        <v>493085</v>
       </c>
       <c r="D102">
-        <v>584906</v>
+        <v>557400</v>
       </c>
       <c r="E102" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2998,16 +3016,16 @@
         <v>106</v>
       </c>
       <c r="B103">
-        <v>636200</v>
+        <v>539000</v>
       </c>
       <c r="C103">
-        <v>555180</v>
+        <v>458463</v>
       </c>
       <c r="D103">
-        <v>627595</v>
+        <v>518262</v>
       </c>
       <c r="E103" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3015,16 +3033,16 @@
         <v>107</v>
       </c>
       <c r="B104">
-        <v>348900</v>
+        <v>276600</v>
       </c>
       <c r="C104">
-        <v>309627</v>
+        <v>244706</v>
       </c>
       <c r="D104">
-        <v>350013</v>
+        <v>276624</v>
       </c>
       <c r="E104" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -3032,16 +3050,16 @@
         <v>108</v>
       </c>
       <c r="B105">
-        <v>350000</v>
+        <v>573800</v>
       </c>
       <c r="C105">
-        <v>309632</v>
+        <v>522772</v>
       </c>
       <c r="D105">
-        <v>350019</v>
+        <v>590960</v>
       </c>
       <c r="E105" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -3049,16 +3067,16 @@
         <v>109</v>
       </c>
       <c r="B106">
-        <v>499160</v>
+        <v>368859</v>
       </c>
       <c r="C106">
-        <v>425217</v>
+        <v>268099</v>
       </c>
       <c r="D106">
-        <v>480680</v>
+        <v>303068</v>
       </c>
       <c r="E106" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3066,16 +3084,16 @@
         <v>110</v>
       </c>
       <c r="B107">
-        <v>321850</v>
+        <v>303000</v>
       </c>
       <c r="C107">
-        <v>274170</v>
+        <v>268099</v>
       </c>
       <c r="D107">
-        <v>309932</v>
+        <v>303068</v>
       </c>
       <c r="E107" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3083,16 +3101,16 @@
         <v>111</v>
       </c>
       <c r="B108">
-        <v>798150</v>
+        <v>505100</v>
       </c>
       <c r="C108">
-        <v>679906</v>
+        <v>460225</v>
       </c>
       <c r="D108">
-        <v>768589</v>
+        <v>520254</v>
       </c>
       <c r="E108" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3100,16 +3118,16 @@
         <v>112</v>
       </c>
       <c r="B109">
-        <v>369900</v>
+        <v>295800</v>
       </c>
       <c r="C109">
-        <v>327291</v>
+        <v>261708</v>
       </c>
       <c r="D109">
-        <v>369981</v>
+        <v>295844</v>
       </c>
       <c r="E109" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3117,16 +3135,16 @@
         <v>113</v>
       </c>
       <c r="B110">
-        <v>254174</v>
+        <v>807600</v>
       </c>
       <c r="C110">
-        <v>686474</v>
+        <v>735882</v>
       </c>
       <c r="D110">
-        <v>776014</v>
+        <v>831866</v>
       </c>
       <c r="E110" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3134,16 +3152,16 @@
         <v>114</v>
       </c>
       <c r="B111">
-        <v>652200</v>
+        <v>170010</v>
       </c>
       <c r="C111">
-        <v>549152</v>
+        <v>742990</v>
       </c>
       <c r="D111">
-        <v>620781</v>
+        <v>839902</v>
       </c>
       <c r="E111" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3151,16 +3169,16 @@
         <v>115</v>
       </c>
       <c r="B112">
-        <v>672900</v>
+        <v>639600</v>
       </c>
       <c r="C112">
-        <v>595263</v>
+        <v>453485</v>
       </c>
       <c r="D112">
-        <v>672906</v>
+        <v>512635</v>
       </c>
       <c r="E112" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3168,16 +3186,16 @@
         <v>116</v>
       </c>
       <c r="B113">
-        <v>368600</v>
+        <v>336300</v>
       </c>
       <c r="C113">
-        <v>326115</v>
+        <v>297525</v>
       </c>
       <c r="D113">
-        <v>368652</v>
+        <v>336333</v>
       </c>
       <c r="E113" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3185,16 +3203,16 @@
         <v>117</v>
       </c>
       <c r="B114">
-        <v>633800</v>
+        <v>692981</v>
       </c>
       <c r="C114">
-        <v>560736</v>
+        <v>644270</v>
       </c>
       <c r="D114">
-        <v>633876</v>
+        <v>728305</v>
       </c>
       <c r="E114" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3202,16 +3220,16 @@
         <v>118</v>
       </c>
       <c r="B115">
-        <v>120437</v>
+        <v>349000</v>
       </c>
       <c r="C115">
-        <v>385495</v>
+        <v>311292</v>
       </c>
       <c r="D115">
-        <v>435777</v>
+        <v>351895</v>
       </c>
       <c r="E115" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3219,16 +3237,16 @@
         <v>119</v>
       </c>
       <c r="B116">
-        <v>567150</v>
+        <v>655416</v>
       </c>
       <c r="C116">
-        <v>501716</v>
+        <v>606901</v>
       </c>
       <c r="D116">
-        <v>567158</v>
+        <v>686062</v>
       </c>
       <c r="E116" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3236,16 +3254,16 @@
         <v>120</v>
       </c>
       <c r="B117">
-        <v>690800</v>
+        <v>457900</v>
       </c>
       <c r="C117">
-        <v>553548</v>
+        <v>333786</v>
       </c>
       <c r="D117">
-        <v>625750</v>
+        <v>377323</v>
       </c>
       <c r="E117" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3253,16 +3271,16 @@
         <v>121</v>
       </c>
       <c r="B118">
-        <v>578400</v>
+        <v>595900</v>
       </c>
       <c r="C118">
-        <v>504759</v>
+        <v>543022</v>
       </c>
       <c r="D118">
-        <v>570597</v>
+        <v>613851</v>
       </c>
       <c r="E118" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3270,16 +3288,16 @@
         <v>122</v>
       </c>
       <c r="B119">
-        <v>645700</v>
+        <v>732300</v>
       </c>
       <c r="C119">
-        <v>563819</v>
+        <v>667236</v>
       </c>
       <c r="D119">
-        <v>637361</v>
+        <v>754267</v>
       </c>
       <c r="E119" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3287,16 +3305,16 @@
         <v>123</v>
       </c>
       <c r="B120">
-        <v>653700</v>
+        <v>577000</v>
       </c>
       <c r="C120">
-        <v>578301</v>
+        <v>416825</v>
       </c>
       <c r="D120">
-        <v>653731</v>
+        <v>471194</v>
       </c>
       <c r="E120" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3304,16 +3322,16 @@
         <v>124</v>
       </c>
       <c r="B121">
-        <v>593670</v>
+        <v>669700</v>
       </c>
       <c r="C121">
-        <v>518008</v>
+        <v>610238</v>
       </c>
       <c r="D121">
-        <v>585575</v>
+        <v>689834</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3321,16 +3339,16 @@
         <v>125</v>
       </c>
       <c r="B122">
-        <v>525210</v>
+        <v>648300</v>
       </c>
       <c r="C122">
-        <v>458284</v>
+        <v>590732</v>
       </c>
       <c r="D122">
-        <v>518060</v>
+        <v>667784</v>
       </c>
       <c r="E122" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3338,16 +3356,16 @@
         <v>126</v>
       </c>
       <c r="B123">
-        <v>515293</v>
+        <v>676900</v>
       </c>
       <c r="C123">
-        <v>549249</v>
+        <v>560655</v>
       </c>
       <c r="D123">
-        <v>620890</v>
+        <v>633784</v>
       </c>
       <c r="E123" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3355,16 +3373,16 @@
         <v>127</v>
       </c>
       <c r="B124">
-        <v>622774</v>
+        <v>553510</v>
       </c>
       <c r="C124">
-        <v>639070</v>
+        <v>496014</v>
       </c>
       <c r="D124">
-        <v>722427</v>
+        <v>560711</v>
       </c>
       <c r="E124" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3372,16 +3390,16 @@
         <v>128</v>
       </c>
       <c r="B125">
-        <v>599400</v>
+        <v>656332</v>
       </c>
       <c r="C125">
-        <v>523383</v>
+        <v>691684</v>
       </c>
       <c r="D125">
-        <v>591651</v>
+        <v>781904</v>
       </c>
       <c r="E125" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3389,16 +3407,16 @@
         <v>129</v>
       </c>
       <c r="B126">
-        <v>691700</v>
+        <v>621700</v>
       </c>
       <c r="C126">
-        <v>582436</v>
+        <v>566473</v>
       </c>
       <c r="D126">
-        <v>658406</v>
+        <v>640361</v>
       </c>
       <c r="E126" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3406,16 +3424,16 @@
         <v>130</v>
       </c>
       <c r="B127">
-        <v>524200</v>
+        <v>678086</v>
       </c>
       <c r="C127">
-        <v>544268</v>
+        <v>630387</v>
       </c>
       <c r="D127">
-        <v>615260</v>
+        <v>712611</v>
       </c>
       <c r="E127" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3423,16 +3441,16 @@
         <v>131</v>
       </c>
       <c r="B128">
-        <v>781500</v>
+        <v>552446</v>
       </c>
       <c r="C128">
-        <v>681874</v>
+        <v>589077</v>
       </c>
       <c r="D128">
-        <v>770815</v>
+        <v>665913</v>
       </c>
       <c r="E128" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3440,16 +3458,16 @@
         <v>132</v>
       </c>
       <c r="B129">
-        <v>842530</v>
+        <v>809900</v>
       </c>
       <c r="C129">
-        <v>828838</v>
+        <v>738012</v>
       </c>
       <c r="D129">
-        <v>936947</v>
+        <v>834275</v>
       </c>
       <c r="E129" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3457,16 +3475,16 @@
         <v>133</v>
       </c>
       <c r="B130">
-        <v>436000</v>
+        <v>968771</v>
       </c>
       <c r="C130">
-        <v>385772</v>
+        <v>897075</v>
       </c>
       <c r="D130">
-        <v>436090</v>
+        <v>1014084</v>
       </c>
       <c r="E130" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3474,16 +3492,16 @@
         <v>134</v>
       </c>
       <c r="B131">
-        <v>697400</v>
+        <v>416300</v>
       </c>
       <c r="C131">
-        <v>616935</v>
+        <v>368237</v>
       </c>
       <c r="D131">
-        <v>697405</v>
+        <v>416267</v>
       </c>
       <c r="E131" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3491,16 +3509,16 @@
         <v>135</v>
       </c>
       <c r="B132">
-        <v>473300</v>
+        <v>676700</v>
       </c>
       <c r="C132">
-        <v>418704</v>
+        <v>534181</v>
       </c>
       <c r="D132">
-        <v>473318</v>
+        <v>603857</v>
       </c>
       <c r="E132" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3508,16 +3526,16 @@
         <v>136</v>
       </c>
       <c r="B133">
-        <v>756900</v>
+        <v>497400</v>
       </c>
       <c r="C133">
-        <v>669634</v>
+        <v>362540</v>
       </c>
       <c r="D133">
-        <v>756978</v>
+        <v>409828</v>
       </c>
       <c r="E133" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3525,16 +3543,16 @@
         <v>137</v>
       </c>
       <c r="B134">
-        <v>489800</v>
+        <v>795400</v>
       </c>
       <c r="C134">
-        <v>433299</v>
+        <v>724764</v>
       </c>
       <c r="D134">
-        <v>489817</v>
+        <v>819298</v>
       </c>
       <c r="E134" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3542,16 +3560,16 @@
         <v>138</v>
       </c>
       <c r="B135">
-        <v>786000</v>
+        <v>514700</v>
       </c>
       <c r="C135">
-        <v>695349</v>
+        <v>468972</v>
       </c>
       <c r="D135">
-        <v>786047</v>
+        <v>530143</v>
       </c>
       <c r="E135" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3559,16 +3577,16 @@
         <v>139</v>
       </c>
       <c r="B136">
-        <v>816000</v>
+        <v>889000</v>
       </c>
       <c r="C136">
-        <v>807257</v>
+        <v>790497</v>
       </c>
       <c r="D136">
-        <v>912552</v>
+        <v>893606</v>
       </c>
       <c r="E136" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3576,16 +3594,16 @@
         <v>140</v>
       </c>
       <c r="B137">
-        <v>290532</v>
+        <v>306187</v>
       </c>
       <c r="C137">
-        <v>889276</v>
+        <v>962488</v>
       </c>
       <c r="D137">
-        <v>1005268</v>
+        <v>1088030</v>
       </c>
       <c r="E137" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3593,16 +3611,16 @@
         <v>141</v>
       </c>
       <c r="B138">
-        <v>881500</v>
+        <v>780000</v>
       </c>
       <c r="C138">
-        <v>742245</v>
+        <v>710767</v>
       </c>
       <c r="D138">
-        <v>839059</v>
+        <v>803476</v>
       </c>
       <c r="E138" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3610,16 +3628,16 @@
         <v>142</v>
       </c>
       <c r="B139">
-        <v>972900</v>
+        <v>908200</v>
       </c>
       <c r="C139">
-        <v>860652</v>
+        <v>803353</v>
       </c>
       <c r="D139">
-        <v>972911</v>
+        <v>908138</v>
       </c>
       <c r="E139" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3627,16 +3645,16 @@
         <v>143</v>
       </c>
       <c r="B140">
-        <v>833400</v>
+        <v>1103200</v>
       </c>
       <c r="C140">
-        <v>737277</v>
+        <v>975866</v>
       </c>
       <c r="D140">
-        <v>833443</v>
+        <v>1103153</v>
       </c>
       <c r="E140" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3644,16 +3662,16 @@
         <v>144</v>
       </c>
       <c r="B141">
-        <v>1021500</v>
+        <v>1006008</v>
       </c>
       <c r="C141">
-        <v>903634</v>
+        <v>931508</v>
       </c>
       <c r="D141">
-        <v>1021499</v>
+        <v>1053009</v>
       </c>
       <c r="E141" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -3661,16 +3679,16 @@
         <v>145</v>
       </c>
       <c r="B142">
-        <v>1086600</v>
+        <v>889900</v>
       </c>
       <c r="C142">
-        <v>1043702</v>
+        <v>797976</v>
       </c>
       <c r="D142">
-        <v>1179837</v>
+        <v>902060</v>
       </c>
       <c r="E142" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3678,16 +3696,16 @@
         <v>146</v>
       </c>
       <c r="B143">
-        <v>923160</v>
+        <v>1244907</v>
       </c>
       <c r="C143">
-        <v>1004037</v>
+        <v>1157394</v>
       </c>
       <c r="D143">
-        <v>1134999</v>
+        <v>1308358</v>
       </c>
       <c r="E143" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3695,16 +3713,16 @@
         <v>147</v>
       </c>
       <c r="B144">
-        <v>410372</v>
+        <v>1051968</v>
       </c>
       <c r="C144">
-        <v>864919</v>
+        <v>978028</v>
       </c>
       <c r="D144">
-        <v>977734</v>
+        <v>1105597</v>
       </c>
       <c r="E144" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3712,16 +3730,16 @@
         <v>148</v>
       </c>
       <c r="B145">
-        <v>714800</v>
+        <v>1215117</v>
       </c>
       <c r="C145">
-        <v>632356</v>
+        <v>1129628</v>
       </c>
       <c r="D145">
-        <v>714837</v>
+        <v>1276971</v>
       </c>
       <c r="E145" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3729,16 +3747,16 @@
         <v>149</v>
       </c>
       <c r="B146">
-        <v>650400</v>
+        <v>972904</v>
       </c>
       <c r="C146">
-        <v>575428</v>
+        <v>1086698</v>
       </c>
       <c r="D146">
-        <v>650484</v>
+        <v>1228442</v>
       </c>
       <c r="E146" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3746,16 +3764,16 @@
         <v>150</v>
       </c>
       <c r="B147">
-        <v>608300</v>
+        <v>341117</v>
       </c>
       <c r="C147">
-        <v>512261</v>
+        <v>910590</v>
       </c>
       <c r="D147">
-        <v>579078</v>
+        <v>1029363</v>
       </c>
       <c r="E147" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3763,16 +3781,16 @@
         <v>151</v>
       </c>
       <c r="B148">
-        <v>594800</v>
+        <v>751200</v>
       </c>
       <c r="C148">
-        <v>526233</v>
+        <v>684417</v>
       </c>
       <c r="D148">
-        <v>594872</v>
+        <v>773688</v>
       </c>
       <c r="E148" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3780,16 +3798,16 @@
         <v>152</v>
       </c>
       <c r="B149">
-        <v>414818</v>
+        <v>669789</v>
       </c>
       <c r="C149">
-        <v>345967</v>
+        <v>622802</v>
       </c>
       <c r="D149">
-        <v>391093</v>
+        <v>704037</v>
       </c>
       <c r="E149" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3797,16 +3815,16 @@
         <v>153</v>
       </c>
       <c r="B150">
-        <v>331700</v>
+        <v>596412</v>
       </c>
       <c r="C150">
-        <v>293472</v>
+        <v>554434</v>
       </c>
       <c r="D150">
-        <v>331752</v>
+        <v>626752</v>
       </c>
       <c r="E150" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3814,16 +3832,16 @@
         <v>154</v>
       </c>
       <c r="B151">
-        <v>702400</v>
+        <v>623089</v>
       </c>
       <c r="C151">
-        <v>621409</v>
+        <v>569557</v>
       </c>
       <c r="D151">
-        <v>702462</v>
+        <v>643847</v>
       </c>
       <c r="E151" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3831,16 +3849,16 @@
         <v>155</v>
       </c>
       <c r="B152">
-        <v>823900</v>
+        <v>301600</v>
       </c>
       <c r="C152">
-        <v>719471</v>
+        <v>280133</v>
       </c>
       <c r="D152">
-        <v>813315</v>
+        <v>316672</v>
       </c>
       <c r="E152" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3848,16 +3866,16 @@
         <v>156</v>
       </c>
       <c r="B153">
-        <v>825200</v>
+        <v>723700</v>
       </c>
       <c r="C153">
-        <v>729992</v>
+        <v>672568</v>
       </c>
       <c r="D153">
-        <v>825208</v>
+        <v>760295</v>
       </c>
       <c r="E153" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3865,16 +3883,16 @@
         <v>157</v>
       </c>
       <c r="B154">
-        <v>674300</v>
+        <v>626300</v>
       </c>
       <c r="C154">
-        <v>588771</v>
+        <v>554013</v>
       </c>
       <c r="D154">
-        <v>665568</v>
+        <v>626275</v>
       </c>
       <c r="E154" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3882,16 +3900,16 @@
         <v>158</v>
       </c>
       <c r="B155">
-        <v>249710</v>
+        <v>863086</v>
       </c>
       <c r="C155">
-        <v>534516</v>
+        <v>778703</v>
       </c>
       <c r="D155">
-        <v>604235</v>
+        <v>880274</v>
       </c>
       <c r="E155" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3899,16 +3917,16 @@
         <v>159</v>
       </c>
       <c r="B156">
-        <v>596700</v>
+        <v>867200</v>
       </c>
       <c r="C156">
-        <v>578852</v>
+        <v>790091</v>
       </c>
       <c r="D156">
-        <v>654355</v>
+        <v>893146</v>
       </c>
       <c r="E156" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3916,16 +3934,16 @@
         <v>160</v>
       </c>
       <c r="B157">
-        <v>650900</v>
+        <v>699400</v>
       </c>
       <c r="C157">
-        <v>575805</v>
+        <v>637244</v>
       </c>
       <c r="D157">
-        <v>650911</v>
+        <v>720363</v>
       </c>
       <c r="E157" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3933,16 +3951,16 @@
         <v>161</v>
       </c>
       <c r="B158">
-        <v>649600</v>
+        <v>263166</v>
       </c>
       <c r="C158">
-        <v>574649</v>
+        <v>485538</v>
       </c>
       <c r="D158">
-        <v>649603</v>
+        <v>548869</v>
       </c>
       <c r="E158" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3950,16 +3968,16 @@
         <v>162</v>
       </c>
       <c r="B159">
-        <v>406600</v>
+        <v>628853</v>
       </c>
       <c r="C159">
-        <v>359652</v>
+        <v>501206</v>
       </c>
       <c r="D159">
-        <v>406563</v>
+        <v>566581</v>
       </c>
       <c r="E159" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3967,16 +3985,16 @@
         <v>163</v>
       </c>
       <c r="B160">
-        <v>552200</v>
+        <v>685973</v>
       </c>
       <c r="C160">
-        <v>488463</v>
+        <v>560889</v>
       </c>
       <c r="D160">
-        <v>552176</v>
+        <v>634049</v>
       </c>
       <c r="E160" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3984,16 +4002,16 @@
         <v>164</v>
       </c>
       <c r="B161">
-        <v>644200</v>
+        <v>682600</v>
       </c>
       <c r="C161">
-        <v>569880</v>
+        <v>621959</v>
       </c>
       <c r="D161">
-        <v>644213</v>
+        <v>703084</v>
       </c>
       <c r="E161" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -4001,16 +4019,16 @@
         <v>165</v>
       </c>
       <c r="B162">
-        <v>606900</v>
+        <v>388000</v>
       </c>
       <c r="C162">
-        <v>536952</v>
+        <v>343304</v>
       </c>
       <c r="D162">
-        <v>606989</v>
+        <v>388083</v>
       </c>
       <c r="E162" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -4018,16 +4036,16 @@
         <v>166</v>
       </c>
       <c r="B163">
-        <v>675391</v>
+        <v>580200</v>
       </c>
       <c r="C163">
-        <v>648506</v>
+        <v>528678</v>
       </c>
       <c r="D163">
-        <v>733094</v>
+        <v>597636</v>
       </c>
       <c r="E163" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -4035,16 +4053,16 @@
         <v>167</v>
       </c>
       <c r="B164">
-        <v>820600</v>
+        <v>676900</v>
       </c>
       <c r="C164">
-        <v>691001</v>
+        <v>616797</v>
       </c>
       <c r="D164">
-        <v>781132</v>
+        <v>697249</v>
       </c>
       <c r="E164" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -4052,16 +4070,16 @@
         <v>168</v>
       </c>
       <c r="B165">
-        <v>793900</v>
+        <v>637800</v>
       </c>
       <c r="C165">
-        <v>702327</v>
+        <v>581159</v>
       </c>
       <c r="D165">
-        <v>793935</v>
+        <v>656962</v>
       </c>
       <c r="E165" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -4069,16 +4087,16 @@
         <v>169</v>
       </c>
       <c r="B166">
-        <v>884900</v>
+        <v>314500</v>
       </c>
       <c r="C166">
-        <v>782861</v>
+        <v>294140</v>
       </c>
       <c r="D166">
-        <v>884973</v>
+        <v>332506</v>
       </c>
       <c r="E166" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -4086,16 +4104,16 @@
         <v>170</v>
       </c>
       <c r="B167">
-        <v>611829</v>
+        <v>711784</v>
       </c>
       <c r="C167">
-        <v>573764</v>
+        <v>701897</v>
       </c>
       <c r="D167">
-        <v>648603</v>
+        <v>793449</v>
       </c>
       <c r="E167" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -4103,16 +4121,16 @@
         <v>171</v>
       </c>
       <c r="B168">
-        <v>178545</v>
+        <v>864818</v>
       </c>
       <c r="C168">
-        <v>635753</v>
+        <v>554002</v>
       </c>
       <c r="D168">
-        <v>718678</v>
+        <v>626263</v>
       </c>
       <c r="E168" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -4120,16 +4138,16 @@
         <v>172</v>
       </c>
       <c r="B169">
-        <v>382700</v>
+        <v>834300</v>
       </c>
       <c r="C169">
-        <v>338495</v>
+        <v>563083</v>
       </c>
       <c r="D169">
-        <v>382647</v>
+        <v>636528</v>
       </c>
       <c r="E169" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -4137,16 +4155,16 @@
         <v>173</v>
       </c>
       <c r="B170">
-        <v>226576</v>
+        <v>929900</v>
       </c>
       <c r="C170">
-        <v>630283</v>
+        <v>627649</v>
       </c>
       <c r="D170">
-        <v>712494</v>
+        <v>709517</v>
       </c>
       <c r="E170" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -4154,16 +4172,16 @@
         <v>174</v>
       </c>
       <c r="B171">
-        <v>577600</v>
+        <v>644797</v>
       </c>
       <c r="C171">
-        <v>510907</v>
+        <v>621001</v>
       </c>
       <c r="D171">
-        <v>577547</v>
+        <v>702001</v>
       </c>
       <c r="E171" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -4171,16 +4189,16 @@
         <v>175</v>
       </c>
       <c r="B172">
-        <v>633719</v>
+        <v>188166</v>
       </c>
       <c r="C172">
-        <v>600672</v>
+        <v>688094</v>
       </c>
       <c r="D172">
-        <v>679021</v>
+        <v>777845</v>
       </c>
       <c r="E172" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -4188,16 +4206,16 @@
         <v>176</v>
       </c>
       <c r="B173">
-        <v>919800</v>
+        <v>365300</v>
       </c>
       <c r="C173">
-        <v>813755</v>
+        <v>323109</v>
       </c>
       <c r="D173">
-        <v>919897</v>
+        <v>365253</v>
       </c>
       <c r="E173" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -4205,16 +4223,16 @@
         <v>177</v>
       </c>
       <c r="B174">
-        <v>952000</v>
+        <v>748700</v>
       </c>
       <c r="C174">
-        <v>842247</v>
+        <v>682174</v>
       </c>
       <c r="D174">
-        <v>952106</v>
+        <v>771153</v>
       </c>
       <c r="E174" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -4222,16 +4240,16 @@
         <v>178</v>
       </c>
       <c r="B175">
-        <v>582667</v>
+        <v>605071</v>
       </c>
       <c r="C175">
-        <v>881321</v>
+        <v>442375</v>
       </c>
       <c r="D175">
-        <v>996276</v>
+        <v>500077</v>
       </c>
       <c r="E175" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -4239,16 +4257,16 @@
         <v>179</v>
       </c>
       <c r="B176">
-        <v>872800</v>
+        <v>713600</v>
       </c>
       <c r="C176">
-        <v>761638</v>
+        <v>650125</v>
       </c>
       <c r="D176">
-        <v>860982</v>
+        <v>734924</v>
       </c>
       <c r="E176" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -4256,16 +4274,16 @@
         <v>180</v>
       </c>
       <c r="B177">
-        <v>963238</v>
+        <v>966600</v>
       </c>
       <c r="C177">
-        <v>971324</v>
+        <v>880750</v>
       </c>
       <c r="D177">
-        <v>1098018</v>
+        <v>995630</v>
       </c>
       <c r="E177" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4273,16 +4291,16 @@
         <v>181</v>
       </c>
       <c r="B178">
-        <v>802500</v>
+        <v>1003298</v>
       </c>
       <c r="C178">
-        <v>709932</v>
+        <v>911588</v>
       </c>
       <c r="D178">
-        <v>802532</v>
+        <v>1030491</v>
       </c>
       <c r="E178" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -4290,16 +4308,16 @@
         <v>182</v>
       </c>
       <c r="B179">
-        <v>959000</v>
+        <v>364700</v>
       </c>
       <c r="C179">
-        <v>691935</v>
+        <v>322590</v>
       </c>
       <c r="D179">
-        <v>782187</v>
+        <v>364667</v>
       </c>
       <c r="E179" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -4307,16 +4325,16 @@
         <v>183</v>
       </c>
       <c r="B180">
-        <v>1043300</v>
+        <v>614064</v>
       </c>
       <c r="C180">
-        <v>922940</v>
+        <v>706589</v>
       </c>
       <c r="D180">
-        <v>1043324</v>
+        <v>798753</v>
       </c>
       <c r="E180" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -4324,16 +4342,16 @@
         <v>184</v>
       </c>
       <c r="B181">
-        <v>774396</v>
+        <v>904700</v>
       </c>
       <c r="C181">
-        <v>725750</v>
+        <v>824342</v>
       </c>
       <c r="D181">
-        <v>820413</v>
+        <v>931865</v>
       </c>
       <c r="E181" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -4341,16 +4359,16 @@
         <v>185</v>
       </c>
       <c r="B182">
-        <v>948100</v>
+        <v>1208736</v>
       </c>
       <c r="C182">
-        <v>827285</v>
+        <v>1051291</v>
       </c>
       <c r="D182">
-        <v>935192</v>
+        <v>1188416</v>
       </c>
       <c r="E182" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -4358,16 +4376,16 @@
         <v>186</v>
       </c>
       <c r="B183">
-        <v>1051700</v>
+        <v>868600</v>
       </c>
       <c r="C183">
-        <v>917737</v>
+        <v>768380</v>
       </c>
       <c r="D183">
-        <v>1037442</v>
+        <v>868603</v>
       </c>
       <c r="E183" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4375,16 +4393,16 @@
         <v>187</v>
       </c>
       <c r="B184">
-        <v>721700</v>
+        <v>1096400</v>
       </c>
       <c r="C184">
-        <v>638431</v>
+        <v>998924</v>
       </c>
       <c r="D184">
-        <v>721704</v>
+        <v>1129219</v>
       </c>
       <c r="E184" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -4392,16 +4410,16 @@
         <v>188</v>
       </c>
       <c r="B185">
-        <v>971922</v>
+        <v>862000</v>
       </c>
       <c r="C185">
-        <v>1007699</v>
+        <v>785499</v>
       </c>
       <c r="D185">
-        <v>1139138</v>
+        <v>887956</v>
       </c>
       <c r="E185" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -4409,16 +4427,16 @@
         <v>189</v>
       </c>
       <c r="B186">
-        <v>233502</v>
+        <v>1090000</v>
       </c>
       <c r="C186">
-        <v>831437</v>
+        <v>993292</v>
       </c>
       <c r="D186">
-        <v>939885</v>
+        <v>1122852</v>
       </c>
       <c r="E186" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -4426,16 +4444,16 @@
         <v>190</v>
       </c>
       <c r="B187">
-        <v>698700</v>
+        <v>758400</v>
       </c>
       <c r="C187">
-        <v>529476</v>
+        <v>690991</v>
       </c>
       <c r="D187">
-        <v>598538</v>
+        <v>781121</v>
       </c>
       <c r="E187" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -4443,16 +4461,16 @@
         <v>191</v>
       </c>
       <c r="B188">
-        <v>788067</v>
+        <v>1024294</v>
       </c>
       <c r="C188">
-        <v>738267</v>
+        <v>1090661</v>
       </c>
       <c r="D188">
-        <v>834562</v>
+        <v>1232922</v>
       </c>
       <c r="E188" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -4460,16 +4478,16 @@
         <v>192</v>
       </c>
       <c r="B189">
-        <v>642803</v>
+        <v>246084</v>
       </c>
       <c r="C189">
-        <v>691935</v>
+        <v>899887</v>
       </c>
       <c r="D189">
-        <v>782187</v>
+        <v>1017264</v>
       </c>
       <c r="E189" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -4477,16 +4495,16 @@
         <v>193</v>
       </c>
       <c r="B190">
-        <v>439200</v>
+        <v>616600</v>
       </c>
       <c r="C190">
-        <v>388512</v>
+        <v>458453</v>
       </c>
       <c r="D190">
-        <v>439188</v>
+        <v>518252</v>
       </c>
       <c r="E190" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -4494,16 +4512,16 @@
         <v>194</v>
       </c>
       <c r="B191">
-        <v>681500</v>
+        <v>859800</v>
       </c>
       <c r="C191">
-        <v>602873</v>
+        <v>799047</v>
       </c>
       <c r="D191">
-        <v>681509</v>
+        <v>903271</v>
       </c>
       <c r="E191" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4511,16 +4529,16 @@
         <v>195</v>
       </c>
       <c r="B192">
-        <v>478300</v>
+        <v>399300</v>
       </c>
       <c r="C192">
-        <v>427174</v>
+        <v>370853</v>
       </c>
       <c r="D192">
-        <v>482893</v>
+        <v>419225</v>
       </c>
       <c r="E192" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -4528,16 +4546,16 @@
         <v>196</v>
       </c>
       <c r="B193">
-        <v>483700</v>
+        <v>748900</v>
       </c>
       <c r="C193">
-        <v>427927</v>
+        <v>522006</v>
       </c>
       <c r="D193">
-        <v>483744</v>
+        <v>590093</v>
       </c>
       <c r="E193" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -4545,16 +4563,16 @@
         <v>197</v>
       </c>
       <c r="B194">
-        <v>733900</v>
+        <v>497500</v>
       </c>
       <c r="C194">
-        <v>649269</v>
+        <v>369874</v>
       </c>
       <c r="D194">
-        <v>733956</v>
+        <v>418119</v>
       </c>
       <c r="E194" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -4562,16 +4580,16 @@
         <v>198</v>
       </c>
       <c r="B195">
-        <v>1045400</v>
+        <v>509764</v>
       </c>
       <c r="C195">
-        <v>691935</v>
+        <v>370526</v>
       </c>
       <c r="D195">
-        <v>782187</v>
+        <v>418856</v>
       </c>
       <c r="E195" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -4579,16 +4597,16 @@
         <v>199</v>
       </c>
       <c r="B196">
-        <v>866100</v>
+        <v>756100</v>
       </c>
       <c r="C196">
-        <v>755764</v>
+        <v>702723</v>
       </c>
       <c r="D196">
-        <v>854342</v>
+        <v>794382</v>
       </c>
       <c r="E196" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -4596,16 +4614,16 @@
         <v>200</v>
       </c>
       <c r="B197">
-        <v>307499</v>
+        <v>974000</v>
       </c>
       <c r="C197">
-        <v>857524</v>
+        <v>905081</v>
       </c>
       <c r="D197">
-        <v>969375</v>
+        <v>1023135</v>
       </c>
       <c r="E197" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -4613,16 +4631,16 @@
         <v>201</v>
       </c>
       <c r="B198">
-        <v>849000</v>
+        <v>903836</v>
       </c>
       <c r="C198">
-        <v>691935</v>
+        <v>817985</v>
       </c>
       <c r="D198">
-        <v>782187</v>
+        <v>924678</v>
       </c>
       <c r="E198" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -4630,16 +4648,16 @@
         <v>202</v>
       </c>
       <c r="B199">
-        <v>279146</v>
+        <v>1088000</v>
       </c>
       <c r="C199">
-        <v>749596</v>
+        <v>1011017</v>
       </c>
       <c r="D199">
-        <v>847370</v>
+        <v>1142889</v>
       </c>
       <c r="E199" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -4647,16 +4665,16 @@
         <v>203</v>
       </c>
       <c r="B200">
-        <v>1155900</v>
+        <v>1109600</v>
       </c>
       <c r="C200">
-        <v>1009339</v>
+        <v>1031247</v>
       </c>
       <c r="D200">
-        <v>1140992</v>
+        <v>1165758</v>
       </c>
       <c r="E200" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -4664,16 +4682,16 @@
         <v>204</v>
       </c>
       <c r="B201">
-        <v>1069000</v>
+        <v>1198600</v>
       </c>
       <c r="C201">
-        <v>1037902</v>
+        <v>970821</v>
       </c>
       <c r="D201">
-        <v>1173281</v>
+        <v>1097450</v>
       </c>
       <c r="E201" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4681,16 +4699,16 @@
         <v>205</v>
       </c>
       <c r="B202">
-        <v>251279</v>
+        <v>945002</v>
       </c>
       <c r="C202">
-        <v>796878</v>
+        <v>878532</v>
       </c>
       <c r="D202">
-        <v>900819</v>
+        <v>993123</v>
       </c>
       <c r="E202" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -4698,16 +4716,16 @@
         <v>206</v>
       </c>
       <c r="B203">
-        <v>1071300</v>
+        <v>1141900</v>
       </c>
       <c r="C203">
-        <v>947743</v>
+        <v>1040415</v>
       </c>
       <c r="D203">
-        <v>1071361</v>
+        <v>1176122</v>
       </c>
       <c r="E203" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -4715,16 +4733,16 @@
         <v>207</v>
       </c>
       <c r="B204">
-        <v>1168700</v>
+        <v>1199000</v>
       </c>
       <c r="C204">
-        <v>1033905</v>
+        <v>1092436</v>
       </c>
       <c r="D204">
-        <v>1168762</v>
+        <v>1234928</v>
       </c>
       <c r="E204" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -4732,16 +4750,16 @@
         <v>208</v>
       </c>
       <c r="B205">
-        <v>918330</v>
+        <v>1258900</v>
       </c>
       <c r="C205">
-        <v>890223</v>
+        <v>1147058</v>
       </c>
       <c r="D205">
-        <v>1006339</v>
+        <v>1296674</v>
       </c>
       <c r="E205" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -4749,16 +4767,16 @@
         <v>209</v>
       </c>
       <c r="B206">
-        <v>1162200</v>
+        <v>1178300</v>
       </c>
       <c r="C206">
-        <v>1028173</v>
+        <v>1059423</v>
       </c>
       <c r="D206">
-        <v>1162283</v>
+        <v>1197609</v>
       </c>
       <c r="E206" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -4766,16 +4784,16 @@
         <v>210</v>
       </c>
       <c r="B207">
-        <v>874400</v>
+        <v>264820</v>
       </c>
       <c r="C207">
-        <v>773565</v>
+        <v>862483</v>
       </c>
       <c r="D207">
-        <v>874465</v>
+        <v>974981</v>
       </c>
       <c r="E207" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4783,16 +4801,16 @@
         <v>211</v>
       </c>
       <c r="B208">
-        <v>696800</v>
+        <v>1125800</v>
       </c>
       <c r="C208">
-        <v>616457</v>
+        <v>1025768</v>
       </c>
       <c r="D208">
-        <v>696865</v>
+        <v>1159564</v>
       </c>
       <c r="E208" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -4800,16 +4818,16 @@
         <v>212</v>
       </c>
       <c r="B209">
-        <v>915007</v>
+        <v>1228000</v>
       </c>
       <c r="C209">
-        <v>1029702</v>
+        <v>1119024</v>
       </c>
       <c r="D209">
-        <v>1164010</v>
+        <v>1264984</v>
       </c>
       <c r="E209" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4817,16 +4835,16 @@
         <v>213</v>
       </c>
       <c r="B210">
-        <v>962071</v>
+        <v>967814</v>
       </c>
       <c r="C210">
-        <v>1005245</v>
+        <v>963513</v>
       </c>
       <c r="D210">
-        <v>1136364</v>
+        <v>1089189</v>
       </c>
       <c r="E210" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4834,16 +4852,16 @@
         <v>214</v>
       </c>
       <c r="B211">
-        <v>1193200</v>
+        <v>1217476</v>
       </c>
       <c r="C211">
-        <v>1055507</v>
+        <v>1112820</v>
       </c>
       <c r="D211">
-        <v>1193182</v>
+        <v>1257971</v>
       </c>
       <c r="E211" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -4851,16 +4869,16 @@
         <v>215</v>
       </c>
       <c r="B212">
-        <v>1043900</v>
+        <v>732300</v>
       </c>
       <c r="C212">
-        <v>911518</v>
+        <v>667209</v>
       </c>
       <c r="D212">
-        <v>1030412</v>
+        <v>754236</v>
       </c>
       <c r="E212" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4868,16 +4886,16 @@
         <v>216</v>
       </c>
       <c r="B213">
-        <v>1039700</v>
+        <v>1223000</v>
       </c>
       <c r="C213">
-        <v>907888</v>
+        <v>928745</v>
       </c>
       <c r="D213">
-        <v>1026308</v>
+        <v>1049886</v>
       </c>
       <c r="E213" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4885,16 +4903,16 @@
         <v>217</v>
       </c>
       <c r="B214">
-        <v>866500</v>
+        <v>1228813</v>
       </c>
       <c r="C214">
-        <v>756580</v>
+        <v>913924</v>
       </c>
       <c r="D214">
-        <v>855265</v>
+        <v>1033132</v>
       </c>
       <c r="E214" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4902,16 +4920,16 @@
         <v>218</v>
       </c>
       <c r="B215">
-        <v>794300</v>
+        <v>1100150</v>
       </c>
       <c r="C215">
-        <v>693526</v>
+        <v>986562</v>
       </c>
       <c r="D215">
-        <v>783986</v>
+        <v>1115244</v>
       </c>
       <c r="E215" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4919,16 +4937,16 @@
         <v>219</v>
       </c>
       <c r="B216">
-        <v>526341</v>
+        <v>1056967</v>
       </c>
       <c r="C216">
-        <v>898522</v>
+        <v>727888</v>
       </c>
       <c r="D216">
-        <v>1015721</v>
+        <v>822830</v>
       </c>
       <c r="E216" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4936,16 +4954,16 @@
         <v>220</v>
       </c>
       <c r="B217">
-        <v>1235900</v>
+        <v>807445</v>
       </c>
       <c r="C217">
-        <v>1093344</v>
+        <v>750623</v>
       </c>
       <c r="D217">
-        <v>1235954</v>
+        <v>848530</v>
       </c>
       <c r="E217" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4953,16 +4971,16 @@
         <v>221</v>
       </c>
       <c r="B218">
-        <v>286045</v>
+        <v>554703</v>
       </c>
       <c r="C218">
-        <v>855787</v>
+        <v>972496</v>
       </c>
       <c r="D218">
-        <v>967412</v>
+        <v>1099343</v>
       </c>
       <c r="E218" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4970,16 +4988,16 @@
         <v>222</v>
       </c>
       <c r="B219">
-        <v>402846</v>
+        <v>404159</v>
       </c>
       <c r="C219">
-        <v>1148476</v>
+        <v>1183357</v>
       </c>
       <c r="D219">
-        <v>1298277</v>
+        <v>1337708</v>
       </c>
       <c r="E219" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4987,16 +5005,16 @@
         <v>223</v>
       </c>
       <c r="B220">
-        <v>1066170</v>
+        <v>301458</v>
       </c>
       <c r="C220">
-        <v>1033628</v>
+        <v>926243</v>
       </c>
       <c r="D220">
-        <v>1168449</v>
+        <v>1047057</v>
       </c>
       <c r="E220" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -5004,16 +5022,16 @@
         <v>224</v>
       </c>
       <c r="B221">
-        <v>411340</v>
+        <v>265346</v>
       </c>
       <c r="C221">
-        <v>1172706</v>
+        <v>1243027</v>
       </c>
       <c r="D221">
-        <v>1325668</v>
+        <v>1405161</v>
       </c>
       <c r="E221" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -5021,16 +5039,16 @@
         <v>225</v>
       </c>
       <c r="B222">
-        <v>1438600</v>
+        <v>1227800</v>
       </c>
       <c r="C222">
-        <v>1255247</v>
+        <v>1118725</v>
       </c>
       <c r="D222">
-        <v>1418975</v>
+        <v>1264645</v>
       </c>
       <c r="E222" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -5038,16 +5056,16 @@
         <v>226</v>
       </c>
       <c r="B223">
-        <v>344179</v>
+        <v>298034</v>
       </c>
       <c r="C223">
-        <v>1091468</v>
+        <v>1269253</v>
       </c>
       <c r="D223">
-        <v>1233834</v>
+        <v>1434808</v>
       </c>
       <c r="E223" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -5055,16 +5073,16 @@
         <v>227</v>
       </c>
       <c r="B224">
-        <v>435382</v>
+        <v>1491000</v>
       </c>
       <c r="C224">
-        <v>1241256</v>
+        <v>1358589</v>
       </c>
       <c r="D224">
-        <v>1403159</v>
+        <v>1535796</v>
       </c>
       <c r="E224" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -5072,16 +5090,16 @@
         <v>228</v>
       </c>
       <c r="B225">
-        <v>443474</v>
+        <v>1296500</v>
       </c>
       <c r="C225">
-        <v>1264331</v>
+        <v>1181327</v>
       </c>
       <c r="D225">
-        <v>1429244</v>
+        <v>1335413</v>
       </c>
       <c r="E225" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -5089,16 +5107,16 @@
         <v>229</v>
       </c>
       <c r="B226">
-        <v>290977</v>
+        <v>1467500</v>
       </c>
       <c r="C226">
-        <v>1181131</v>
+        <v>1337120</v>
       </c>
       <c r="D226">
-        <v>1335191</v>
+        <v>1511527</v>
       </c>
       <c r="E226" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -5106,16 +5124,16 @@
         <v>230</v>
       </c>
       <c r="B227">
-        <v>704900</v>
+        <v>458843</v>
       </c>
       <c r="C227">
-        <v>646290</v>
+        <v>1343446</v>
       </c>
       <c r="D227">
-        <v>730589</v>
+        <v>1518678</v>
       </c>
       <c r="E227" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -5123,16 +5141,16 @@
         <v>231</v>
       </c>
       <c r="B228">
-        <v>845900</v>
+        <v>1094656</v>
       </c>
       <c r="C228">
-        <v>748318</v>
+        <v>1013663</v>
       </c>
       <c r="D228">
-        <v>845924</v>
+        <v>1145880</v>
       </c>
       <c r="E228" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -5140,16 +5158,16 @@
         <v>232</v>
       </c>
       <c r="B229">
-        <v>878782</v>
+        <v>306657</v>
       </c>
       <c r="C229">
-        <v>1319254</v>
+        <v>946957</v>
       </c>
       <c r="D229">
-        <v>1491331</v>
+        <v>1070474</v>
       </c>
       <c r="E229" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -5157,16 +5175,16 @@
         <v>233</v>
       </c>
       <c r="B230">
-        <v>1471017</v>
+        <v>753000</v>
       </c>
       <c r="C230">
-        <v>1037902</v>
+        <v>559598</v>
       </c>
       <c r="D230">
-        <v>1173281</v>
+        <v>632589</v>
       </c>
       <c r="E230" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -5174,16 +5192,16 @@
         <v>234</v>
       </c>
       <c r="B231">
-        <v>1042900</v>
+        <v>752500</v>
       </c>
       <c r="C231">
-        <v>922580</v>
+        <v>559597</v>
       </c>
       <c r="D231">
-        <v>1042916</v>
+        <v>632588</v>
       </c>
       <c r="E231" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -5191,16 +5209,16 @@
         <v>235</v>
       </c>
       <c r="B232">
-        <v>543997</v>
+        <v>871400</v>
       </c>
       <c r="C232">
-        <v>1550914</v>
+        <v>809925</v>
       </c>
       <c r="D232">
-        <v>1753207</v>
+        <v>915568</v>
       </c>
       <c r="E232" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -5208,16 +5226,16 @@
         <v>236</v>
       </c>
       <c r="B233">
-        <v>1615162</v>
+        <v>926136</v>
       </c>
       <c r="C233">
-        <v>1550914</v>
+        <v>1427866</v>
       </c>
       <c r="D233">
-        <v>1753207</v>
+        <v>1614110</v>
       </c>
       <c r="E233" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -5225,16 +5243,16 @@
         <v>237</v>
       </c>
       <c r="B234">
-        <v>320617</v>
+        <v>1550282</v>
       </c>
       <c r="C234">
-        <v>1462511</v>
+        <v>1328492</v>
       </c>
       <c r="D234">
-        <v>1653273</v>
+        <v>1501774</v>
       </c>
       <c r="E234" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -5242,16 +5260,16 @@
         <v>238</v>
       </c>
       <c r="B235">
-        <v>411625</v>
+        <v>1099096</v>
       </c>
       <c r="C235">
-        <v>1231468</v>
+        <v>1001479</v>
       </c>
       <c r="D235">
-        <v>1392094</v>
+        <v>1132106</v>
       </c>
       <c r="E235" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -5259,16 +5277,16 @@
         <v>239</v>
       </c>
       <c r="B236">
-        <v>188264</v>
+        <v>358319</v>
       </c>
       <c r="C236">
-        <v>691935</v>
+        <v>1678598</v>
       </c>
       <c r="D236">
-        <v>782187</v>
+        <v>1897545</v>
       </c>
       <c r="E236" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -5276,16 +5294,16 @@
         <v>240</v>
       </c>
       <c r="B237">
-        <v>839226</v>
+        <v>1842300</v>
       </c>
       <c r="C237">
-        <v>980241</v>
+        <v>1678598</v>
       </c>
       <c r="D237">
-        <v>1108099</v>
+        <v>1897545</v>
       </c>
       <c r="E237" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -5293,16 +5311,16 @@
         <v>241</v>
       </c>
       <c r="B238">
-        <v>1477000</v>
+        <v>540631</v>
       </c>
       <c r="C238">
-        <v>1271757</v>
+        <v>1582917</v>
       </c>
       <c r="D238">
-        <v>1437638</v>
+        <v>1789384</v>
       </c>
       <c r="E238" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -5310,16 +5328,16 @@
         <v>242</v>
       </c>
       <c r="B239">
-        <v>1268752</v>
+        <v>1462800</v>
       </c>
       <c r="C239">
-        <v>1095564</v>
+        <v>1332852</v>
       </c>
       <c r="D239">
-        <v>1238463</v>
+        <v>1506703</v>
       </c>
       <c r="E239" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -5327,16 +5345,16 @@
         <v>243</v>
       </c>
       <c r="B240">
-        <v>251358</v>
+        <v>198409</v>
       </c>
       <c r="C240">
-        <v>1275387</v>
+        <v>715342</v>
       </c>
       <c r="D240">
-        <v>1441742</v>
+        <v>808647</v>
       </c>
       <c r="E240" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -5344,16 +5362,16 @@
         <v>244</v>
       </c>
       <c r="B241">
-        <v>1453505</v>
+        <v>884448</v>
       </c>
       <c r="C241">
-        <v>1118393</v>
+        <v>1027700</v>
       </c>
       <c r="D241">
-        <v>1264270</v>
+        <v>1161748</v>
       </c>
       <c r="E241" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -5361,16 +5379,16 @@
         <v>245</v>
       </c>
       <c r="B242">
-        <v>1079300</v>
+        <v>1480533</v>
       </c>
       <c r="C242">
-        <v>942487</v>
+        <v>1376458</v>
       </c>
       <c r="D242">
-        <v>1065420</v>
+        <v>1555996</v>
       </c>
       <c r="E242" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -5378,16 +5396,16 @@
         <v>246</v>
       </c>
       <c r="B243">
-        <v>1389000</v>
+        <v>343339</v>
       </c>
       <c r="C243">
-        <v>1309015</v>
+        <v>1124109</v>
       </c>
       <c r="D243">
-        <v>1479756</v>
+        <v>1270732</v>
       </c>
       <c r="E243" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -5395,16 +5413,16 @@
         <v>247</v>
       </c>
       <c r="B244">
-        <v>1141400</v>
+        <v>264902</v>
       </c>
       <c r="C244">
-        <v>995987</v>
+        <v>1380387</v>
       </c>
       <c r="D244">
-        <v>1125898</v>
+        <v>1560438</v>
       </c>
       <c r="E244" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -5412,16 +5430,16 @@
         <v>248</v>
       </c>
       <c r="B245">
-        <v>1004428</v>
+        <v>1531827</v>
       </c>
       <c r="C245">
-        <v>922580</v>
+        <v>1210468</v>
       </c>
       <c r="D245">
-        <v>1042916</v>
+        <v>1368355</v>
       </c>
       <c r="E245" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -5429,16 +5447,16 @@
         <v>249</v>
       </c>
       <c r="B246">
-        <v>1504000</v>
+        <v>806000</v>
       </c>
       <c r="C246">
-        <v>1294390</v>
+        <v>793406</v>
       </c>
       <c r="D246">
-        <v>1463223</v>
+        <v>896894</v>
       </c>
       <c r="E246" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -5446,16 +5464,16 @@
         <v>250</v>
       </c>
       <c r="B247">
-        <v>325411</v>
+        <v>1259400</v>
       </c>
       <c r="C247">
-        <v>1484371</v>
+        <v>1180673</v>
       </c>
       <c r="D247">
-        <v>1677984</v>
+        <v>1334674</v>
       </c>
       <c r="E247" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -5463,16 +5481,16 @@
         <v>251</v>
       </c>
       <c r="B248">
-        <v>1158420</v>
+        <v>1058552</v>
       </c>
       <c r="C248">
-        <v>1464856</v>
+        <v>1141538</v>
       </c>
       <c r="D248">
-        <v>1655924</v>
+        <v>1290434</v>
       </c>
       <c r="E248" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -5480,16 +5498,16 @@
         <v>252</v>
       </c>
       <c r="B249">
-        <v>902760</v>
+        <v>1537600</v>
       </c>
       <c r="C249">
-        <v>1355227</v>
+        <v>1400954</v>
       </c>
       <c r="D249">
-        <v>1531996</v>
+        <v>1583688</v>
       </c>
       <c r="E249" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -5497,16 +5515,16 @@
         <v>253</v>
       </c>
       <c r="B250">
-        <v>959000</v>
+        <v>342946</v>
       </c>
       <c r="C250">
-        <v>980241</v>
+        <v>1606576</v>
       </c>
       <c r="D250">
-        <v>1108099</v>
+        <v>1816130</v>
       </c>
       <c r="E250" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -5514,16 +5532,16 @@
         <v>254</v>
       </c>
       <c r="B251">
-        <v>987697</v>
+        <v>1220842</v>
       </c>
       <c r="C251">
-        <v>1055331</v>
+        <v>1585455</v>
       </c>
       <c r="D251">
-        <v>1192982</v>
+        <v>1792253</v>
       </c>
       <c r="E251" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -5531,16 +5549,16 @@
         <v>255</v>
       </c>
       <c r="B252">
-        <v>1039000</v>
+        <v>951405</v>
       </c>
       <c r="C252">
-        <v>920403</v>
+        <v>1466800</v>
       </c>
       <c r="D252">
-        <v>1040456</v>
+        <v>1658122</v>
       </c>
       <c r="E252" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -5548,16 +5566,16 @@
         <v>256</v>
       </c>
       <c r="B253">
-        <v>973016</v>
+        <v>1178300</v>
       </c>
       <c r="C253">
-        <v>812683</v>
+        <v>1010035</v>
       </c>
       <c r="D253">
-        <v>918685</v>
+        <v>1141779</v>
       </c>
       <c r="E253" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -5565,16 +5583,16 @@
         <v>257</v>
       </c>
       <c r="B254">
-        <v>949900</v>
+        <v>1040919</v>
       </c>
       <c r="C254">
-        <v>840347</v>
+        <v>1142214</v>
       </c>
       <c r="D254">
-        <v>949958</v>
+        <v>1291198</v>
       </c>
       <c r="E254" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -5582,16 +5600,16 @@
         <v>258</v>
       </c>
       <c r="B255">
-        <v>261356</v>
+        <v>874700</v>
       </c>
       <c r="C255">
-        <v>1326115</v>
+        <v>796943</v>
       </c>
       <c r="D255">
-        <v>1499087</v>
+        <v>900892</v>
       </c>
       <c r="E255" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -5599,16 +5617,16 @@
         <v>259</v>
       </c>
       <c r="B256">
-        <v>327506</v>
+        <v>299008</v>
       </c>
       <c r="C256">
-        <v>1037902</v>
+        <v>703671</v>
       </c>
       <c r="D256">
-        <v>1173281</v>
+        <v>795455</v>
       </c>
       <c r="E256" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -5616,16 +5634,16 @@
         <v>260</v>
       </c>
       <c r="B257">
-        <v>1413000</v>
+        <v>998200</v>
       </c>
       <c r="C257">
-        <v>1049435</v>
+        <v>909532</v>
       </c>
       <c r="D257">
-        <v>1186318</v>
+        <v>1028166</v>
       </c>
       <c r="E257" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -5633,16 +5651,16 @@
         <v>261</v>
       </c>
       <c r="B258">
-        <v>911915</v>
+        <v>988910</v>
       </c>
       <c r="C258">
-        <v>1288241</v>
+        <v>1435292</v>
       </c>
       <c r="D258">
-        <v>1456272</v>
+        <v>1622504</v>
       </c>
       <c r="E258" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -5650,16 +5668,16 @@
         <v>262</v>
       </c>
       <c r="B259">
-        <v>911915</v>
+        <v>1327895</v>
       </c>
       <c r="C259">
-        <v>980241</v>
+        <v>1332282</v>
       </c>
       <c r="D259">
-        <v>1108099</v>
+        <v>1506057</v>
       </c>
       <c r="E259" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -5667,16 +5685,16 @@
         <v>263</v>
       </c>
       <c r="B260">
-        <v>519639</v>
+        <v>1351354</v>
       </c>
       <c r="C260">
-        <v>1481470</v>
+        <v>1268849</v>
       </c>
       <c r="D260">
-        <v>1674705</v>
+        <v>1434351</v>
       </c>
       <c r="E260" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -5684,16 +5702,16 @@
         <v>264</v>
       </c>
       <c r="B261">
-        <v>905000</v>
+        <v>1032400</v>
       </c>
       <c r="C261">
-        <v>1371102</v>
+        <v>940636</v>
       </c>
       <c r="D261">
-        <v>1549941</v>
+        <v>1063328</v>
       </c>
       <c r="E261" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -5701,16 +5719,16 @@
         <v>265</v>
       </c>
       <c r="B262">
-        <v>1137739</v>
+        <v>1251400</v>
       </c>
       <c r="C262">
-        <v>1327132</v>
+        <v>1140175</v>
       </c>
       <c r="D262">
-        <v>1500236</v>
+        <v>1288894</v>
       </c>
       <c r="E262" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -5718,16 +5736,16 @@
         <v>266</v>
       </c>
       <c r="B263">
-        <v>1110500</v>
+        <v>961054</v>
       </c>
       <c r="C263">
-        <v>946015</v>
+        <v>1032832</v>
       </c>
       <c r="D263">
-        <v>1069409</v>
+        <v>1167549</v>
       </c>
       <c r="E263" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -5735,16 +5753,16 @@
         <v>267</v>
       </c>
       <c r="B264">
-        <v>951800</v>
+        <v>961054</v>
       </c>
       <c r="C264">
-        <v>810871</v>
+        <v>1032832</v>
       </c>
       <c r="D264">
-        <v>916637</v>
+        <v>1167549</v>
       </c>
       <c r="E264" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -5752,16 +5770,16 @@
         <v>268</v>
       </c>
       <c r="B265">
-        <v>1076811</v>
+        <v>814350</v>
       </c>
       <c r="C265">
-        <v>1008836</v>
+        <v>1483982</v>
       </c>
       <c r="D265">
-        <v>1140423</v>
+        <v>1677545</v>
       </c>
       <c r="E265" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -5769,16 +5787,16 @@
         <v>269</v>
       </c>
       <c r="B266">
-        <v>335676</v>
+        <v>1576400</v>
       </c>
       <c r="C266">
-        <v>1703212</v>
+        <v>1436392</v>
       </c>
       <c r="D266">
-        <v>1925370</v>
+        <v>1623747</v>
       </c>
       <c r="E266" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -5786,16 +5804,16 @@
         <v>270</v>
       </c>
       <c r="B267">
-        <v>1773922</v>
+        <v>998000</v>
       </c>
       <c r="C267">
-        <v>1822159</v>
+        <v>819119</v>
       </c>
       <c r="D267">
-        <v>2059832</v>
+        <v>925961</v>
       </c>
       <c r="E267" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -5803,16 +5821,16 @@
         <v>271</v>
       </c>
       <c r="B268">
-        <v>565584</v>
+        <v>919000</v>
       </c>
       <c r="C268">
-        <v>1793612</v>
+        <v>877629</v>
       </c>
       <c r="D268">
-        <v>2027562</v>
+        <v>992102</v>
       </c>
       <c r="E268" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -5820,16 +5838,16 @@
         <v>272</v>
       </c>
       <c r="B269">
-        <v>1749500</v>
+        <v>835900</v>
       </c>
       <c r="C269">
-        <v>1547666</v>
+        <v>761983</v>
       </c>
       <c r="D269">
-        <v>1749536</v>
+        <v>861373</v>
       </c>
       <c r="E269" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -5837,16 +5855,16 @@
         <v>273</v>
       </c>
       <c r="B270">
-        <v>1214400</v>
+        <v>1318300</v>
       </c>
       <c r="C270">
-        <v>1060423</v>
+        <v>1201081</v>
       </c>
       <c r="D270">
-        <v>1198739</v>
+        <v>1357744</v>
       </c>
       <c r="E270" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -5854,16 +5872,16 @@
         <v>274</v>
       </c>
       <c r="B271">
-        <v>425381</v>
+        <v>1300000</v>
       </c>
       <c r="C271">
-        <v>1726696</v>
+        <v>1184906</v>
       </c>
       <c r="D271">
-        <v>1951917</v>
+        <v>1339459</v>
       </c>
       <c r="E271" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -5871,16 +5889,16 @@
         <v>275</v>
       </c>
       <c r="B272">
-        <v>324313</v>
+        <v>1198400</v>
       </c>
       <c r="C272">
-        <v>1095564</v>
+        <v>1091892</v>
       </c>
       <c r="D272">
-        <v>1238463</v>
+        <v>1234312</v>
       </c>
       <c r="E272" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -5888,16 +5906,16 @@
         <v>276</v>
       </c>
       <c r="B273">
-        <v>446649</v>
+        <v>2164500</v>
       </c>
       <c r="C273">
-        <v>1554032</v>
+        <v>1972174</v>
       </c>
       <c r="D273">
-        <v>1756732</v>
+        <v>2229414</v>
       </c>
       <c r="E273" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5905,16 +5923,16 @@
         <v>277</v>
       </c>
       <c r="B274">
-        <v>1179278</v>
+        <v>596061</v>
       </c>
       <c r="C274">
-        <v>1539511</v>
+        <v>1941277</v>
       </c>
       <c r="D274">
-        <v>1740317</v>
+        <v>2194487</v>
       </c>
       <c r="E274" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5922,16 +5940,16 @@
         <v>278</v>
       </c>
       <c r="B275">
-        <v>1281300</v>
+        <v>3676800</v>
       </c>
       <c r="C275">
-        <v>1118746</v>
+        <v>1675082</v>
       </c>
       <c r="D275">
-        <v>1264670</v>
+        <v>1893571</v>
       </c>
       <c r="E275" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5939,16 +5957,16 @@
         <v>279</v>
       </c>
       <c r="B276">
-        <v>1070509</v>
+        <v>1234511</v>
       </c>
       <c r="C276">
-        <v>1513109</v>
+        <v>1147726</v>
       </c>
       <c r="D276">
-        <v>1710471</v>
+        <v>1297430</v>
       </c>
       <c r="E276" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5956,16 +5974,16 @@
         <v>280</v>
       </c>
       <c r="B277">
-        <v>1251337</v>
+        <v>2051000</v>
       </c>
       <c r="C277">
-        <v>1230621</v>
+        <v>1868851</v>
       </c>
       <c r="D277">
-        <v>1391137</v>
+        <v>2112614</v>
       </c>
       <c r="E277" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5973,16 +5991,16 @@
         <v>281</v>
       </c>
       <c r="B278">
-        <v>352487</v>
+        <v>341789</v>
       </c>
       <c r="C278">
-        <v>1037902</v>
+        <v>1319323</v>
       </c>
       <c r="D278">
-        <v>1173281</v>
+        <v>1491409</v>
       </c>
       <c r="E278" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5990,16 +6008,16 @@
         <v>282</v>
       </c>
       <c r="B279">
-        <v>1379000</v>
+        <v>470717</v>
       </c>
       <c r="C279">
-        <v>1383870</v>
+        <v>1681972</v>
       </c>
       <c r="D279">
-        <v>1564375</v>
+        <v>1901360</v>
       </c>
       <c r="E279" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -6007,16 +6025,16 @@
         <v>283</v>
       </c>
       <c r="B280">
-        <v>1691000</v>
+        <v>1242823</v>
       </c>
       <c r="C280">
-        <v>1455442</v>
+        <v>1666256</v>
       </c>
       <c r="D280">
-        <v>1645282</v>
+        <v>1883594</v>
       </c>
       <c r="E280" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -6024,16 +6042,16 @@
         <v>284</v>
       </c>
       <c r="B281">
-        <v>1143486</v>
+        <v>1328900</v>
       </c>
       <c r="C281">
-        <v>980241</v>
+        <v>1210851</v>
       </c>
       <c r="D281">
-        <v>1108099</v>
+        <v>1368788</v>
       </c>
       <c r="E281" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -6041,16 +6059,16 @@
         <v>285</v>
       </c>
       <c r="B282">
-        <v>407271</v>
+        <v>1128194</v>
       </c>
       <c r="C282">
-        <v>1153225</v>
+        <v>1213117</v>
       </c>
       <c r="D282">
-        <v>1303646</v>
+        <v>1371350</v>
       </c>
       <c r="E282" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -6058,16 +6076,16 @@
         <v>286</v>
       </c>
       <c r="B283">
-        <v>1194000</v>
+        <v>1465936</v>
       </c>
       <c r="C283">
-        <v>1095564</v>
+        <v>1331936</v>
       </c>
       <c r="D283">
-        <v>1238463</v>
+        <v>1505667</v>
       </c>
       <c r="E283" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -6075,16 +6093,16 @@
         <v>287</v>
       </c>
       <c r="B284">
-        <v>1796000</v>
+        <v>371480</v>
       </c>
       <c r="C284">
-        <v>1546259</v>
+        <v>1059436</v>
       </c>
       <c r="D284">
-        <v>1747945</v>
+        <v>1197623</v>
       </c>
       <c r="E284" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -6092,16 +6110,16 @@
         <v>288</v>
       </c>
       <c r="B285">
-        <v>1194000</v>
+        <v>1309300</v>
       </c>
       <c r="C285">
-        <v>1095564</v>
+        <v>1430961</v>
       </c>
       <c r="D285">
-        <v>1238463</v>
+        <v>1617608</v>
       </c>
       <c r="E285" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -6109,16 +6127,16 @@
         <v>289</v>
       </c>
       <c r="B286">
-        <v>1916500</v>
+        <v>336257</v>
       </c>
       <c r="C286">
-        <v>1268548</v>
+        <v>1575265</v>
       </c>
       <c r="D286">
-        <v>1434010</v>
+        <v>1780735</v>
       </c>
       <c r="E286" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -6126,16 +6144,16 @@
         <v>290</v>
       </c>
       <c r="B287">
-        <v>812250</v>
+        <v>4820411</v>
       </c>
       <c r="C287">
-        <v>1130160</v>
+        <v>1124109</v>
       </c>
       <c r="D287">
-        <v>1277573</v>
+        <v>1270732</v>
       </c>
       <c r="E287" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -6143,16 +6161,16 @@
         <v>291</v>
       </c>
       <c r="B288">
-        <v>171615</v>
+        <v>3751198</v>
       </c>
       <c r="C288">
-        <v>701077</v>
+        <v>1687067</v>
       </c>
       <c r="D288">
-        <v>792522</v>
+        <v>1907119</v>
       </c>
       <c r="E288" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -6160,16 +6178,118 @@
         <v>292</v>
       </c>
       <c r="B289">
-        <v>329900</v>
+        <v>1490330</v>
       </c>
       <c r="C289">
-        <v>288306</v>
+        <v>1325409</v>
       </c>
       <c r="D289">
-        <v>325911</v>
+        <v>1498289</v>
       </c>
       <c r="E289" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" t="s">
+        <v>293</v>
+      </c>
+      <c r="B290">
+        <v>1439746</v>
+      </c>
+      <c r="C290">
+        <v>1227294</v>
+      </c>
+      <c r="D290">
+        <v>1387376</v>
+      </c>
+      <c r="E290" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" t="s">
         <v>294</v>
+      </c>
+      <c r="B291">
+        <v>321165</v>
+      </c>
+      <c r="C291">
+        <v>1673560</v>
+      </c>
+      <c r="D291">
+        <v>1891850</v>
+      </c>
+      <c r="E291" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" t="s">
+        <v>295</v>
+      </c>
+      <c r="B292">
+        <v>1309300</v>
+      </c>
+      <c r="C292">
+        <v>1380396</v>
+      </c>
+      <c r="D292">
+        <v>1560447</v>
+      </c>
+      <c r="E292" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" t="s">
+        <v>296</v>
+      </c>
+      <c r="B293">
+        <v>857500</v>
+      </c>
+      <c r="C293">
+        <v>1517121</v>
+      </c>
+      <c r="D293">
+        <v>1715006</v>
+      </c>
+      <c r="E293" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" t="s">
+        <v>297</v>
+      </c>
+      <c r="B294">
+        <v>180863</v>
+      </c>
+      <c r="C294">
+        <v>727458</v>
+      </c>
+      <c r="D294">
+        <v>822344</v>
+      </c>
+      <c r="E294" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" t="s">
+        <v>298</v>
+      </c>
+      <c r="B295">
+        <v>346500</v>
+      </c>
+      <c r="C295">
+        <v>306575</v>
+      </c>
+      <c r="D295">
+        <v>346563</v>
+      </c>
+      <c r="E295" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
